--- a/Data/Final_BW.xlsx
+++ b/Data/Final_BW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Donahue Lab\Desktop\GitHub\biofac\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mayapowell/Documents/Silbiger Lab/Repositories/biofac/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD3E733-B6C8-4E45-B3F1-61B56B1403D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16712D18-B5C5-A545-AC6E-2972EFFA2CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="27140" windowHeight="15360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3742" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3809" uniqueCount="767">
   <si>
     <t>sample_ID</t>
   </si>
@@ -2318,13 +2318,22 @@
   </si>
   <si>
     <t>B19_1_3SP</t>
+  </si>
+  <si>
+    <t>A19_1_3SP</t>
+  </si>
+  <si>
+    <t>A24_1_FAKE</t>
+  </si>
+  <si>
+    <t>A17_1_3SP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2337,6 +2346,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2359,8 +2374,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2642,13 +2658,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G577"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2671,7 +2687,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>323</v>
       </c>
@@ -2694,7 +2710,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>342</v>
       </c>
@@ -2717,7 +2733,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>358</v>
       </c>
@@ -2740,7 +2756,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>374</v>
       </c>
@@ -2763,7 +2779,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>390</v>
       </c>
@@ -2786,7 +2802,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>406</v>
       </c>
@@ -2809,7 +2825,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>325</v>
       </c>
@@ -2832,7 +2848,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>343</v>
       </c>
@@ -2855,7 +2871,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>359</v>
       </c>
@@ -2878,7 +2894,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>375</v>
       </c>
@@ -2901,7 +2917,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>391</v>
       </c>
@@ -2924,7 +2940,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>407</v>
       </c>
@@ -2947,7 +2963,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>326</v>
       </c>
@@ -2970,7 +2986,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>344</v>
       </c>
@@ -2993,7 +3009,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>360</v>
       </c>
@@ -3016,7 +3032,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>376</v>
       </c>
@@ -3039,7 +3055,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>392</v>
       </c>
@@ -3062,7 +3078,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>408</v>
       </c>
@@ -3085,7 +3101,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>327</v>
       </c>
@@ -3108,7 +3124,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>345</v>
       </c>
@@ -3131,7 +3147,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>361</v>
       </c>
@@ -3154,7 +3170,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>377</v>
       </c>
@@ -3177,7 +3193,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>393</v>
       </c>
@@ -3200,7 +3216,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>409</v>
       </c>
@@ -3223,7 +3239,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>418</v>
       </c>
@@ -3246,7 +3262,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>438</v>
       </c>
@@ -3269,7 +3285,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>454</v>
       </c>
@@ -3292,7 +3308,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>470</v>
       </c>
@@ -3315,7 +3331,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>486</v>
       </c>
@@ -3338,7 +3354,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>502</v>
       </c>
@@ -3361,7 +3377,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>420</v>
       </c>
@@ -3384,7 +3400,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>439</v>
       </c>
@@ -3407,7 +3423,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>455</v>
       </c>
@@ -3430,7 +3446,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>471</v>
       </c>
@@ -3453,7 +3469,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>487</v>
       </c>
@@ -3476,7 +3492,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>503</v>
       </c>
@@ -3499,7 +3515,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>421</v>
       </c>
@@ -3522,7 +3538,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>440</v>
       </c>
@@ -3545,7 +3561,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>456</v>
       </c>
@@ -3568,7 +3584,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>472</v>
       </c>
@@ -3591,7 +3607,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>488</v>
       </c>
@@ -3614,7 +3630,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>504</v>
       </c>
@@ -3637,7 +3653,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>422</v>
       </c>
@@ -3660,7 +3676,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>441</v>
       </c>
@@ -3683,7 +3699,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>457</v>
       </c>
@@ -3706,7 +3722,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>473</v>
       </c>
@@ -3729,7 +3745,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>489</v>
       </c>
@@ -3752,7 +3768,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>505</v>
       </c>
@@ -3775,7 +3791,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>433</v>
       </c>
@@ -3798,7 +3814,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>450</v>
       </c>
@@ -3821,7 +3837,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>466</v>
       </c>
@@ -3844,7 +3860,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>482</v>
       </c>
@@ -3867,7 +3883,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>498</v>
       </c>
@@ -3890,7 +3906,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>514</v>
       </c>
@@ -3913,7 +3929,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>435</v>
       </c>
@@ -3936,7 +3952,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>451</v>
       </c>
@@ -3959,7 +3975,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>467</v>
       </c>
@@ -3982,7 +3998,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>483</v>
       </c>
@@ -4005,7 +4021,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>499</v>
       </c>
@@ -4028,7 +4044,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>515</v>
       </c>
@@ -4051,7 +4067,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>436</v>
       </c>
@@ -4074,7 +4090,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>452</v>
       </c>
@@ -4097,7 +4113,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>468</v>
       </c>
@@ -4120,7 +4136,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>484</v>
       </c>
@@ -4143,7 +4159,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>500</v>
       </c>
@@ -4166,7 +4182,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>516</v>
       </c>
@@ -4189,7 +4205,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>437</v>
       </c>
@@ -4212,7 +4228,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>453</v>
       </c>
@@ -4235,7 +4251,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>469</v>
       </c>
@@ -4258,7 +4274,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>485</v>
       </c>
@@ -4281,7 +4297,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>501</v>
       </c>
@@ -4304,7 +4320,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>517</v>
       </c>
@@ -4327,7 +4343,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>518</v>
       </c>
@@ -4350,7 +4366,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>521</v>
       </c>
@@ -4373,7 +4389,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>522</v>
       </c>
@@ -4396,7 +4412,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>523</v>
       </c>
@@ -4419,7 +4435,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>539</v>
       </c>
@@ -4442,7 +4458,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>542</v>
       </c>
@@ -4465,7 +4481,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>544</v>
       </c>
@@ -4488,7 +4504,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>546</v>
       </c>
@@ -4511,7 +4527,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>572</v>
       </c>
@@ -4534,7 +4550,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>575</v>
       </c>
@@ -4557,7 +4573,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>577</v>
       </c>
@@ -4580,7 +4596,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>579</v>
       </c>
@@ -4603,7 +4619,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>605</v>
       </c>
@@ -4626,7 +4642,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>608</v>
       </c>
@@ -4649,7 +4665,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>610</v>
       </c>
@@ -4672,7 +4688,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>612</v>
       </c>
@@ -4695,7 +4711,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>638</v>
       </c>
@@ -4718,7 +4734,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>641</v>
       </c>
@@ -4741,7 +4757,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>643</v>
       </c>
@@ -4764,7 +4780,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>645</v>
       </c>
@@ -4787,7 +4803,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>671</v>
       </c>
@@ -4810,7 +4826,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>674</v>
       </c>
@@ -4833,7 +4849,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>676</v>
       </c>
@@ -4856,7 +4872,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>678</v>
       </c>
@@ -4879,7 +4895,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>37</v>
       </c>
@@ -4902,7 +4918,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>40</v>
       </c>
@@ -4925,7 +4941,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>42</v>
       </c>
@@ -4948,7 +4964,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>44</v>
       </c>
@@ -4971,7 +4987,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>72</v>
       </c>
@@ -4994,7 +5010,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>74</v>
       </c>
@@ -5017,7 +5033,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>76</v>
       </c>
@@ -5040,7 +5056,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>78</v>
       </c>
@@ -5063,7 +5079,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>106</v>
       </c>
@@ -5086,7 +5102,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>108</v>
       </c>
@@ -5109,7 +5125,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>110</v>
       </c>
@@ -5132,7 +5148,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>112</v>
       </c>
@@ -5155,7 +5171,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>140</v>
       </c>
@@ -5178,7 +5194,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>142</v>
       </c>
@@ -5201,7 +5217,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>144</v>
       </c>
@@ -5224,7 +5240,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>146</v>
       </c>
@@ -5247,7 +5263,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>174</v>
       </c>
@@ -5270,7 +5286,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>176</v>
       </c>
@@ -5293,7 +5309,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>178</v>
       </c>
@@ -5316,7 +5332,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>180</v>
       </c>
@@ -5339,7 +5355,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>208</v>
       </c>
@@ -5362,7 +5378,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>210</v>
       </c>
@@ -5385,7 +5401,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>212</v>
       </c>
@@ -5408,7 +5424,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>214</v>
       </c>
@@ -5431,7 +5447,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>534</v>
       </c>
@@ -5454,7 +5470,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>536</v>
       </c>
@@ -5477,7 +5493,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>537</v>
       </c>
@@ -5500,7 +5516,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>538</v>
       </c>
@@ -5523,7 +5539,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>564</v>
       </c>
@@ -5546,7 +5562,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>566</v>
       </c>
@@ -5569,7 +5585,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>568</v>
       </c>
@@ -5592,7 +5608,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>570</v>
       </c>
@@ -5615,7 +5631,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>597</v>
       </c>
@@ -5638,7 +5654,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>599</v>
       </c>
@@ -5661,7 +5677,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>601</v>
       </c>
@@ -5684,7 +5700,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>603</v>
       </c>
@@ -5707,7 +5723,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>630</v>
       </c>
@@ -5730,7 +5746,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>632</v>
       </c>
@@ -5753,7 +5769,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>634</v>
       </c>
@@ -5776,7 +5792,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>636</v>
       </c>
@@ -5799,7 +5815,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>663</v>
       </c>
@@ -5822,7 +5838,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>665</v>
       </c>
@@ -5845,7 +5861,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>667</v>
       </c>
@@ -5868,7 +5884,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>669</v>
       </c>
@@ -5891,7 +5907,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>696</v>
       </c>
@@ -5914,7 +5930,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>698</v>
       </c>
@@ -5937,7 +5953,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>700</v>
       </c>
@@ -5960,7 +5976,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>702</v>
       </c>
@@ -5983,7 +5999,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>529</v>
       </c>
@@ -6006,7 +6022,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>531</v>
       </c>
@@ -6029,7 +6045,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>532</v>
       </c>
@@ -6052,7 +6068,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>533</v>
       </c>
@@ -6075,7 +6091,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>556</v>
       </c>
@@ -6098,7 +6114,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>558</v>
       </c>
@@ -6121,7 +6137,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>560</v>
       </c>
@@ -6144,7 +6160,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>562</v>
       </c>
@@ -6167,7 +6183,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>589</v>
       </c>
@@ -6190,7 +6206,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>591</v>
       </c>
@@ -6213,7 +6229,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>593</v>
       </c>
@@ -6236,7 +6252,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>595</v>
       </c>
@@ -6259,7 +6275,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>622</v>
       </c>
@@ -6282,7 +6298,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>624</v>
       </c>
@@ -6305,7 +6321,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>626</v>
       </c>
@@ -6328,7 +6344,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>628</v>
       </c>
@@ -6351,7 +6367,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>655</v>
       </c>
@@ -6374,7 +6390,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>657</v>
       </c>
@@ -6397,7 +6413,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>659</v>
       </c>
@@ -6420,7 +6436,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>661</v>
       </c>
@@ -6443,7 +6459,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>688</v>
       </c>
@@ -6466,7 +6482,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>690</v>
       </c>
@@ -6489,7 +6505,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>692</v>
       </c>
@@ -6512,7 +6528,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>694</v>
       </c>
@@ -6535,7 +6551,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>19</v>
       </c>
@@ -6558,7 +6574,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>22</v>
       </c>
@@ -6581,7 +6597,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>24</v>
       </c>
@@ -6604,7 +6620,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>26</v>
       </c>
@@ -6627,7 +6643,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>56</v>
       </c>
@@ -6650,7 +6666,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>58</v>
       </c>
@@ -6673,7 +6689,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>60</v>
       </c>
@@ -6696,7 +6712,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>62</v>
       </c>
@@ -6719,7 +6735,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>90</v>
       </c>
@@ -6742,7 +6758,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>92</v>
       </c>
@@ -6765,7 +6781,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>94</v>
       </c>
@@ -6788,7 +6804,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>96</v>
       </c>
@@ -6811,7 +6827,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>124</v>
       </c>
@@ -6834,7 +6850,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>126</v>
       </c>
@@ -6857,7 +6873,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>128</v>
       </c>
@@ -6880,7 +6896,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>130</v>
       </c>
@@ -6903,7 +6919,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>158</v>
       </c>
@@ -6926,7 +6942,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>160</v>
       </c>
@@ -6949,7 +6965,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>162</v>
       </c>
@@ -6972,7 +6988,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>164</v>
       </c>
@@ -6995,7 +7011,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>192</v>
       </c>
@@ -7018,7 +7034,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>194</v>
       </c>
@@ -7041,7 +7057,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>196</v>
       </c>
@@ -7064,7 +7080,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>198</v>
       </c>
@@ -7087,7 +7103,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>704</v>
       </c>
@@ -7110,7 +7126,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>706</v>
       </c>
@@ -7133,7 +7149,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>707</v>
       </c>
@@ -7156,7 +7172,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>708</v>
       </c>
@@ -7179,7 +7195,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>724</v>
       </c>
@@ -7202,7 +7218,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>727</v>
       </c>
@@ -7225,7 +7241,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>729</v>
       </c>
@@ -7248,7 +7264,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>731</v>
       </c>
@@ -7271,7 +7287,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>572</v>
       </c>
@@ -7294,7 +7310,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>575</v>
       </c>
@@ -7317,7 +7333,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>577</v>
       </c>
@@ -7340,7 +7356,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>579</v>
       </c>
@@ -7363,7 +7379,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>605</v>
       </c>
@@ -7386,7 +7402,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>608</v>
       </c>
@@ -7409,7 +7425,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>610</v>
       </c>
@@ -7432,7 +7448,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>612</v>
       </c>
@@ -7455,7 +7471,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>638</v>
       </c>
@@ -7478,7 +7494,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>641</v>
       </c>
@@ -7501,7 +7517,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>643</v>
       </c>
@@ -7524,7 +7540,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>645</v>
       </c>
@@ -7547,7 +7563,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>671</v>
       </c>
@@ -7570,7 +7586,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>674</v>
       </c>
@@ -7593,7 +7609,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>676</v>
       </c>
@@ -7616,7 +7632,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>678</v>
       </c>
@@ -7639,7 +7655,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>333</v>
       </c>
@@ -7662,7 +7678,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>350</v>
       </c>
@@ -7685,7 +7701,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>366</v>
       </c>
@@ -7708,7 +7724,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>382</v>
       </c>
@@ -7731,7 +7747,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>398</v>
       </c>
@@ -7754,7 +7770,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>414</v>
       </c>
@@ -7777,7 +7793,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>335</v>
       </c>
@@ -7800,7 +7816,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>351</v>
       </c>
@@ -7823,7 +7839,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>367</v>
       </c>
@@ -7846,7 +7862,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>383</v>
       </c>
@@ -7869,7 +7885,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>399</v>
       </c>
@@ -7892,7 +7908,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>415</v>
       </c>
@@ -7915,7 +7931,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>336</v>
       </c>
@@ -7938,7 +7954,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>352</v>
       </c>
@@ -7961,7 +7977,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>368</v>
       </c>
@@ -7984,7 +8000,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>384</v>
       </c>
@@ -8007,7 +8023,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>400</v>
       </c>
@@ -8030,7 +8046,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>416</v>
       </c>
@@ -8053,7 +8069,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>337</v>
       </c>
@@ -8076,7 +8092,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>353</v>
       </c>
@@ -8099,7 +8115,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>369</v>
       </c>
@@ -8122,7 +8138,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>385</v>
       </c>
@@ -8145,7 +8161,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>401</v>
       </c>
@@ -8168,7 +8184,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>417</v>
       </c>
@@ -8191,7 +8207,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>232</v>
       </c>
@@ -8214,7 +8230,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>281</v>
       </c>
@@ -8237,7 +8253,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>234</v>
       </c>
@@ -8260,7 +8276,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>282</v>
       </c>
@@ -8283,7 +8299,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>235</v>
       </c>
@@ -8306,7 +8322,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>283</v>
       </c>
@@ -8329,7 +8345,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>236</v>
       </c>
@@ -8352,7 +8368,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>284</v>
       </c>
@@ -8375,7 +8391,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>249</v>
       </c>
@@ -8398,7 +8414,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>297</v>
       </c>
@@ -8421,7 +8437,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>250</v>
       </c>
@@ -8444,7 +8460,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>298</v>
       </c>
@@ -8467,7 +8483,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>251</v>
       </c>
@@ -8490,7 +8506,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>299</v>
       </c>
@@ -8513,7 +8529,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>252</v>
       </c>
@@ -8536,7 +8552,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>300</v>
       </c>
@@ -8559,7 +8575,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>265</v>
       </c>
@@ -8582,7 +8598,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>313</v>
       </c>
@@ -8605,7 +8621,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>266</v>
       </c>
@@ -8628,7 +8644,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>314</v>
       </c>
@@ -8651,7 +8667,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>267</v>
       </c>
@@ -8674,7 +8690,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>315</v>
       </c>
@@ -8697,7 +8713,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>268</v>
       </c>
@@ -8720,7 +8736,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>316</v>
       </c>
@@ -8743,7 +8759,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>7</v>
       </c>
@@ -8766,7 +8782,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>13</v>
       </c>
@@ -8789,7 +8805,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>15</v>
       </c>
@@ -8812,7 +8828,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>17</v>
       </c>
@@ -8835,7 +8851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>46</v>
       </c>
@@ -8858,7 +8874,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>50</v>
       </c>
@@ -8881,7 +8897,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>52</v>
       </c>
@@ -8904,7 +8920,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>54</v>
       </c>
@@ -8927,7 +8943,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>80</v>
       </c>
@@ -8950,7 +8966,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>84</v>
       </c>
@@ -8973,7 +8989,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>86</v>
       </c>
@@ -8996,7 +9012,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>88</v>
       </c>
@@ -9019,7 +9035,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>114</v>
       </c>
@@ -9042,7 +9058,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>118</v>
       </c>
@@ -9065,7 +9081,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>120</v>
       </c>
@@ -9088,7 +9104,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>122</v>
       </c>
@@ -9111,7 +9127,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>148</v>
       </c>
@@ -9134,7 +9150,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>152</v>
       </c>
@@ -9157,7 +9173,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>154</v>
       </c>
@@ -9180,7 +9196,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>156</v>
       </c>
@@ -9203,7 +9219,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>182</v>
       </c>
@@ -9226,7 +9242,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>186</v>
       </c>
@@ -9249,7 +9265,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>188</v>
       </c>
@@ -9272,7 +9288,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>190</v>
       </c>
@@ -9295,7 +9311,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>317</v>
       </c>
@@ -9318,7 +9334,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>338</v>
       </c>
@@ -9341,7 +9357,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>354</v>
       </c>
@@ -9364,7 +9380,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>370</v>
       </c>
@@ -9387,7 +9403,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>386</v>
       </c>
@@ -9410,7 +9426,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>402</v>
       </c>
@@ -9433,7 +9449,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>320</v>
       </c>
@@ -9456,7 +9472,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>339</v>
       </c>
@@ -9479,7 +9495,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>355</v>
       </c>
@@ -9502,7 +9518,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>371</v>
       </c>
@@ -9525,7 +9541,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>387</v>
       </c>
@@ -9548,7 +9564,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>403</v>
       </c>
@@ -9571,7 +9587,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>321</v>
       </c>
@@ -9594,7 +9610,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>340</v>
       </c>
@@ -9617,7 +9633,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>356</v>
       </c>
@@ -9640,7 +9656,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>372</v>
       </c>
@@ -9663,7 +9679,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>388</v>
       </c>
@@ -9686,7 +9702,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>404</v>
       </c>
@@ -9709,7 +9725,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>322</v>
       </c>
@@ -9732,7 +9748,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>341</v>
       </c>
@@ -9755,7 +9771,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>357</v>
       </c>
@@ -9778,7 +9794,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>373</v>
       </c>
@@ -9801,7 +9817,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>389</v>
       </c>
@@ -9824,7 +9840,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>405</v>
       </c>
@@ -9847,7 +9863,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>423</v>
       </c>
@@ -9870,7 +9886,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>442</v>
       </c>
@@ -9893,7 +9909,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>458</v>
       </c>
@@ -9916,7 +9932,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>474</v>
       </c>
@@ -9939,7 +9955,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>490</v>
       </c>
@@ -9962,7 +9978,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>506</v>
       </c>
@@ -9985,7 +10001,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>425</v>
       </c>
@@ -10008,7 +10024,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>443</v>
       </c>
@@ -10031,7 +10047,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>459</v>
       </c>
@@ -10054,7 +10070,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>475</v>
       </c>
@@ -10077,7 +10093,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>491</v>
       </c>
@@ -10100,7 +10116,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>507</v>
       </c>
@@ -10123,7 +10139,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>426</v>
       </c>
@@ -10146,7 +10162,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>444</v>
       </c>
@@ -10169,7 +10185,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>460</v>
       </c>
@@ -10192,7 +10208,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>476</v>
       </c>
@@ -10215,7 +10231,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>492</v>
       </c>
@@ -10238,7 +10254,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>508</v>
       </c>
@@ -10261,7 +10277,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>427</v>
       </c>
@@ -10284,7 +10300,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>445</v>
       </c>
@@ -10307,7 +10323,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>461</v>
       </c>
@@ -10330,7 +10346,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>477</v>
       </c>
@@ -10353,7 +10369,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>493</v>
       </c>
@@ -10376,7 +10392,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>509</v>
       </c>
@@ -10399,7 +10415,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>222</v>
       </c>
@@ -10422,7 +10438,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>273</v>
       </c>
@@ -10445,7 +10461,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>224</v>
       </c>
@@ -10468,7 +10484,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>274</v>
       </c>
@@ -10491,7 +10507,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>225</v>
       </c>
@@ -10514,7 +10530,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>275</v>
       </c>
@@ -10537,7 +10553,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>226</v>
       </c>
@@ -10560,7 +10576,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>276</v>
       </c>
@@ -10583,7 +10599,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>241</v>
       </c>
@@ -10606,7 +10622,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>289</v>
       </c>
@@ -10629,7 +10645,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>242</v>
       </c>
@@ -10652,7 +10668,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>290</v>
       </c>
@@ -10675,7 +10691,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>243</v>
       </c>
@@ -10698,7 +10714,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>291</v>
       </c>
@@ -10721,7 +10737,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>244</v>
       </c>
@@ -10744,7 +10760,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>292</v>
       </c>
@@ -10767,7 +10783,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>257</v>
       </c>
@@ -10790,7 +10806,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>305</v>
       </c>
@@ -10813,7 +10829,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>258</v>
       </c>
@@ -10836,7 +10852,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>306</v>
       </c>
@@ -10859,7 +10875,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>259</v>
       </c>
@@ -10882,7 +10898,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>307</v>
       </c>
@@ -10905,7 +10921,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>260</v>
       </c>
@@ -10928,7 +10944,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>308</v>
       </c>
@@ -10951,7 +10967,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>714</v>
       </c>
@@ -10974,7 +10990,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>716</v>
       </c>
@@ -10997,7 +11013,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>717</v>
       </c>
@@ -11020,7 +11036,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>718</v>
       </c>
@@ -11043,7 +11059,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>741</v>
       </c>
@@ -11066,7 +11082,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>743</v>
       </c>
@@ -11089,7 +11105,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>745</v>
       </c>
@@ -11112,7 +11128,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>747</v>
       </c>
@@ -11135,7 +11151,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>589</v>
       </c>
@@ -11158,7 +11174,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>591</v>
       </c>
@@ -11181,7 +11197,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>593</v>
       </c>
@@ -11204,7 +11220,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>595</v>
       </c>
@@ -11227,7 +11243,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>622</v>
       </c>
@@ -11250,7 +11266,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>624</v>
       </c>
@@ -11273,7 +11289,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>626</v>
       </c>
@@ -11296,7 +11312,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>628</v>
       </c>
@@ -11319,7 +11335,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>655</v>
       </c>
@@ -11342,7 +11358,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>657</v>
       </c>
@@ -11365,7 +11381,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>659</v>
       </c>
@@ -11388,7 +11404,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>661</v>
       </c>
@@ -11411,7 +11427,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>688</v>
       </c>
@@ -11434,7 +11450,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>690</v>
       </c>
@@ -11457,7 +11473,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>692</v>
       </c>
@@ -11480,7 +11496,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>694</v>
       </c>
@@ -11503,7 +11519,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>28</v>
       </c>
@@ -11526,7 +11542,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>31</v>
       </c>
@@ -11549,7 +11565,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>33</v>
       </c>
@@ -11572,7 +11588,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>35</v>
       </c>
@@ -11595,7 +11611,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>64</v>
       </c>
@@ -11618,7 +11634,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>66</v>
       </c>
@@ -11641,7 +11657,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>68</v>
       </c>
@@ -11664,7 +11680,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>70</v>
       </c>
@@ -11687,7 +11703,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>98</v>
       </c>
@@ -11710,7 +11726,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>100</v>
       </c>
@@ -11733,7 +11749,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>102</v>
       </c>
@@ -11756,7 +11772,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>104</v>
       </c>
@@ -11779,7 +11795,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>132</v>
       </c>
@@ -11802,7 +11818,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>134</v>
       </c>
@@ -11825,7 +11841,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>136</v>
       </c>
@@ -11848,7 +11864,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>138</v>
       </c>
@@ -11871,7 +11887,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>166</v>
       </c>
@@ -11894,7 +11910,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>168</v>
       </c>
@@ -11917,7 +11933,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>170</v>
       </c>
@@ -11940,7 +11956,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>172</v>
       </c>
@@ -11963,7 +11979,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>200</v>
       </c>
@@ -11986,7 +12002,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>202</v>
       </c>
@@ -12009,7 +12025,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>204</v>
       </c>
@@ -12032,7 +12048,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>206</v>
       </c>
@@ -12055,7 +12071,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>328</v>
       </c>
@@ -12078,7 +12094,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
         <v>346</v>
       </c>
@@ -12101,7 +12117,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>362</v>
       </c>
@@ -12124,7 +12140,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>378</v>
       </c>
@@ -12147,7 +12163,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>394</v>
       </c>
@@ -12170,7 +12186,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>410</v>
       </c>
@@ -12193,7 +12209,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>330</v>
       </c>
@@ -12216,7 +12232,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>347</v>
       </c>
@@ -12239,7 +12255,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>363</v>
       </c>
@@ -12262,7 +12278,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>379</v>
       </c>
@@ -12285,7 +12301,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>395</v>
       </c>
@@ -12308,7 +12324,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>411</v>
       </c>
@@ -12331,7 +12347,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>331</v>
       </c>
@@ -12354,7 +12370,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>348</v>
       </c>
@@ -12377,7 +12393,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>364</v>
       </c>
@@ -12400,7 +12416,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>380</v>
       </c>
@@ -12423,7 +12439,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>396</v>
       </c>
@@ -12446,7 +12462,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>412</v>
       </c>
@@ -12469,7 +12485,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>332</v>
       </c>
@@ -12492,7 +12508,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>349</v>
       </c>
@@ -12515,7 +12531,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>365</v>
       </c>
@@ -12538,7 +12554,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>381</v>
       </c>
@@ -12561,7 +12577,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>397</v>
       </c>
@@ -12584,7 +12600,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>413</v>
       </c>
@@ -12607,7 +12623,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>719</v>
       </c>
@@ -12630,7 +12646,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>721</v>
       </c>
@@ -12653,7 +12669,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>722</v>
       </c>
@@ -12676,7 +12692,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>723</v>
       </c>
@@ -12699,7 +12715,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>749</v>
       </c>
@@ -12722,7 +12738,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>751</v>
       </c>
@@ -12745,7 +12761,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>753</v>
       </c>
@@ -12768,7 +12784,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>755</v>
       </c>
@@ -12791,7 +12807,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>597</v>
       </c>
@@ -12814,7 +12830,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>599</v>
       </c>
@@ -12837,7 +12853,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>601</v>
       </c>
@@ -12860,7 +12876,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>603</v>
       </c>
@@ -12883,7 +12899,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>630</v>
       </c>
@@ -12906,7 +12922,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>632</v>
       </c>
@@ -12929,7 +12945,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>634</v>
       </c>
@@ -12952,7 +12968,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>636</v>
       </c>
@@ -12975,7 +12991,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>663</v>
       </c>
@@ -12998,7 +13014,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>665</v>
       </c>
@@ -13021,7 +13037,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>667</v>
       </c>
@@ -13044,7 +13060,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>669</v>
       </c>
@@ -13067,7 +13083,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>696</v>
       </c>
@@ -13090,7 +13106,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
         <v>698</v>
       </c>
@@ -13113,7 +13129,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>700</v>
       </c>
@@ -13136,7 +13152,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>702</v>
       </c>
@@ -13159,7 +13175,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
         <v>227</v>
       </c>
@@ -13182,7 +13198,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>277</v>
       </c>
@@ -13205,7 +13221,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>229</v>
       </c>
@@ -13228,7 +13244,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>278</v>
       </c>
@@ -13251,7 +13267,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
         <v>230</v>
       </c>
@@ -13274,7 +13290,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
         <v>279</v>
       </c>
@@ -13297,7 +13313,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
         <v>231</v>
       </c>
@@ -13320,7 +13336,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
         <v>280</v>
       </c>
@@ -13343,7 +13359,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
         <v>245</v>
       </c>
@@ -13366,7 +13382,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
         <v>293</v>
       </c>
@@ -13389,7 +13405,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
         <v>246</v>
       </c>
@@ -13412,7 +13428,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
         <v>294</v>
       </c>
@@ -13435,7 +13451,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>247</v>
       </c>
@@ -13458,7 +13474,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>295</v>
       </c>
@@ -13481,7 +13497,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>248</v>
       </c>
@@ -13504,7 +13520,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
         <v>296</v>
       </c>
@@ -13527,7 +13543,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
         <v>261</v>
       </c>
@@ -13550,7 +13566,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
         <v>309</v>
       </c>
@@ -13573,7 +13589,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
         <v>262</v>
       </c>
@@ -13596,7 +13612,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>310</v>
       </c>
@@ -13619,7 +13635,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>263</v>
       </c>
@@ -13642,7 +13658,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>311</v>
       </c>
@@ -13665,7 +13681,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>264</v>
       </c>
@@ -13688,7 +13704,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>312</v>
       </c>
@@ -13711,7 +13727,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>428</v>
       </c>
@@ -13734,7 +13750,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>446</v>
       </c>
@@ -13757,7 +13773,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>462</v>
       </c>
@@ -13780,7 +13796,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>478</v>
       </c>
@@ -13803,7 +13819,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>494</v>
       </c>
@@ -13826,7 +13842,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>510</v>
       </c>
@@ -13849,7 +13865,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>430</v>
       </c>
@@ -13872,7 +13888,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>447</v>
       </c>
@@ -13895,7 +13911,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>463</v>
       </c>
@@ -13918,7 +13934,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>479</v>
       </c>
@@ -13941,7 +13957,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>495</v>
       </c>
@@ -13964,7 +13980,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>511</v>
       </c>
@@ -13987,7 +14003,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>431</v>
       </c>
@@ -14010,7 +14026,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>448</v>
       </c>
@@ -14033,7 +14049,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>464</v>
       </c>
@@ -14056,7 +14072,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>480</v>
       </c>
@@ -14079,7 +14095,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>496</v>
       </c>
@@ -14102,7 +14118,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>512</v>
       </c>
@@ -14125,7 +14141,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>432</v>
       </c>
@@ -14148,7 +14164,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
         <v>449</v>
       </c>
@@ -14171,7 +14187,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
         <v>465</v>
       </c>
@@ -14194,7 +14210,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
         <v>481</v>
       </c>
@@ -14217,7 +14233,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
         <v>497</v>
       </c>
@@ -14240,7 +14256,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
         <v>513</v>
       </c>
@@ -14263,7 +14279,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>524</v>
       </c>
@@ -14286,7 +14302,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>526</v>
       </c>
@@ -14309,7 +14325,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>527</v>
       </c>
@@ -14332,7 +14348,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
         <v>528</v>
       </c>
@@ -14355,7 +14371,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
         <v>548</v>
       </c>
@@ -14378,7 +14394,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
         <v>550</v>
       </c>
@@ -14401,7 +14417,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
         <v>552</v>
       </c>
@@ -14424,7 +14440,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
         <v>554</v>
       </c>
@@ -14447,7 +14463,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
         <v>581</v>
       </c>
@@ -14470,7 +14486,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
         <v>583</v>
       </c>
@@ -14493,7 +14509,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
         <v>585</v>
       </c>
@@ -14516,7 +14532,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
         <v>587</v>
       </c>
@@ -14539,7 +14555,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
         <v>614</v>
       </c>
@@ -14562,7 +14578,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
         <v>616</v>
       </c>
@@ -14585,7 +14601,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
         <v>618</v>
       </c>
@@ -14608,7 +14624,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
         <v>620</v>
       </c>
@@ -14631,7 +14647,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
         <v>647</v>
       </c>
@@ -14654,7 +14670,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
         <v>649</v>
       </c>
@@ -14677,7 +14693,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
         <v>651</v>
       </c>
@@ -14700,7 +14716,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
         <v>653</v>
       </c>
@@ -14723,7 +14739,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
         <v>680</v>
       </c>
@@ -14746,7 +14762,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
         <v>682</v>
       </c>
@@ -14769,7 +14785,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
         <v>684</v>
       </c>
@@ -14792,7 +14808,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
         <v>686</v>
       </c>
@@ -14815,7 +14831,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
         <v>709</v>
       </c>
@@ -14838,7 +14854,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
         <v>711</v>
       </c>
@@ -14861,7 +14877,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
         <v>712</v>
       </c>
@@ -14884,7 +14900,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
         <v>713</v>
       </c>
@@ -14907,7 +14923,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
         <v>733</v>
       </c>
@@ -14930,7 +14946,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
         <v>735</v>
       </c>
@@ -14953,7 +14969,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
         <v>737</v>
       </c>
@@ -14976,7 +14992,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
         <v>739</v>
       </c>
@@ -14999,7 +15015,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
         <v>581</v>
       </c>
@@ -15022,7 +15038,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
         <v>583</v>
       </c>
@@ -15045,7 +15061,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
         <v>585</v>
       </c>
@@ -15068,7 +15084,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
         <v>587</v>
       </c>
@@ -15091,7 +15107,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
         <v>614</v>
       </c>
@@ -15114,7 +15130,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
         <v>616</v>
       </c>
@@ -15137,7 +15153,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
         <v>618</v>
       </c>
@@ -15160,7 +15176,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
         <v>620</v>
       </c>
@@ -15183,7 +15199,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
         <v>647</v>
       </c>
@@ -15206,7 +15222,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
         <v>649</v>
       </c>
@@ -15229,7 +15245,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
         <v>651</v>
       </c>
@@ -15252,7 +15268,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
         <v>653</v>
       </c>
@@ -15275,7 +15291,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
         <v>680</v>
       </c>
@@ -15298,7 +15314,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
         <v>682</v>
       </c>
@@ -15321,7 +15337,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
         <v>684</v>
       </c>
@@ -15344,7 +15360,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
         <v>686</v>
       </c>
@@ -15367,7 +15383,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
         <v>216</v>
       </c>
@@ -15390,7 +15406,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
         <v>269</v>
       </c>
@@ -15413,7 +15429,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
         <v>219</v>
       </c>
@@ -15436,7 +15452,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
         <v>270</v>
       </c>
@@ -15459,7 +15475,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="558" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
         <v>220</v>
       </c>
@@ -15482,7 +15498,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
         <v>271</v>
       </c>
@@ -15505,7 +15521,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
         <v>221</v>
       </c>
@@ -15528,7 +15544,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
         <v>272</v>
       </c>
@@ -15551,7 +15567,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
         <v>237</v>
       </c>
@@ -15574,7 +15590,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
         <v>285</v>
       </c>
@@ -15597,7 +15613,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
         <v>238</v>
       </c>
@@ -15620,7 +15636,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
         <v>286</v>
       </c>
@@ -15643,7 +15659,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
         <v>239</v>
       </c>
@@ -15666,7 +15682,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
         <v>287</v>
       </c>
@@ -15689,7 +15705,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
         <v>240</v>
       </c>
@@ -15712,7 +15728,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
         <v>288</v>
       </c>
@@ -15735,7 +15751,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
         <v>253</v>
       </c>
@@ -15758,7 +15774,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
         <v>301</v>
       </c>
@@ -15781,7 +15797,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
         <v>254</v>
       </c>
@@ -15804,7 +15820,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
         <v>302</v>
       </c>
@@ -15827,7 +15843,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
         <v>255</v>
       </c>
@@ -15850,7 +15866,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
         <v>303</v>
       </c>
@@ -15873,7 +15889,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="576" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
         <v>256</v>
       </c>
@@ -15896,7 +15912,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
         <v>304</v>
       </c>
@@ -15930,13 +15946,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D93EAE40-CB66-4677-8B60-FAEB87FECE43}">
-  <dimension ref="A1:D154"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F191"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>757</v>
       </c>
@@ -15950,7 +15969,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>760</v>
       </c>
@@ -15961,7 +15980,7 @@
         <v>74.994600000000005</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>325</v>
       </c>
@@ -15972,7 +15991,7 @@
         <v>10.173</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -15983,7 +16002,7 @@
         <v>13.6996</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>761</v>
       </c>
@@ -15994,7 +16013,7 @@
         <v>18.021899999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>220</v>
       </c>
@@ -16005,7 +16024,7 @@
         <v>8.1714000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -16016,7 +16035,7 @@
         <v>9.4723000000000006</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>243</v>
       </c>
@@ -16027,7 +16046,7 @@
         <v>11.8279</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>717</v>
       </c>
@@ -16038,7 +16057,7 @@
         <v>8.2769999999999992</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>760</v>
       </c>
@@ -16049,7 +16068,7 @@
         <v>74.992099999999994</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>422</v>
       </c>
@@ -16060,7 +16079,7 @@
         <v>11.6334</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>244</v>
       </c>
@@ -16071,7 +16090,7 @@
         <v>12.891400000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>423</v>
       </c>
@@ -16082,7 +16101,7 @@
         <v>10.247</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>760</v>
       </c>
@@ -16093,7 +16112,7 @@
         <v>74.9863</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>323</v>
       </c>
@@ -16107,7 +16126,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>342</v>
       </c>
@@ -16121,7 +16140,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>358</v>
       </c>
@@ -16135,7 +16154,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>374</v>
       </c>
@@ -16149,7 +16168,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>390</v>
       </c>
@@ -16163,7 +16182,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>406</v>
       </c>
@@ -16177,7 +16196,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>343</v>
       </c>
@@ -16191,7 +16210,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>359</v>
       </c>
@@ -16205,7 +16224,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>375</v>
       </c>
@@ -16219,7 +16238,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>391</v>
       </c>
@@ -16233,7 +16252,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>407</v>
       </c>
@@ -16247,7 +16266,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>326</v>
       </c>
@@ -16261,7 +16280,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>344</v>
       </c>
@@ -16275,7 +16294,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>360</v>
       </c>
@@ -16289,7 +16308,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>376</v>
       </c>
@@ -16303,7 +16322,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>392</v>
       </c>
@@ -16317,7 +16336,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>408</v>
       </c>
@@ -16331,7 +16350,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>327</v>
       </c>
@@ -16345,7 +16364,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>345</v>
       </c>
@@ -16359,7 +16378,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>361</v>
       </c>
@@ -16373,7 +16392,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>377</v>
       </c>
@@ -16387,7 +16406,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>393</v>
       </c>
@@ -16401,7 +16420,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>409</v>
       </c>
@@ -16415,7 +16434,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>7</v>
       </c>
@@ -16429,7 +16448,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -16443,7 +16462,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>46</v>
       </c>
@@ -16457,7 +16476,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -16471,7 +16490,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>52</v>
       </c>
@@ -16485,7 +16504,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>54</v>
       </c>
@@ -16499,7 +16518,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>80</v>
       </c>
@@ -16513,7 +16532,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>84</v>
       </c>
@@ -16527,7 +16546,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>86</v>
       </c>
@@ -16541,7 +16560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>88</v>
       </c>
@@ -16555,7 +16574,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>114</v>
       </c>
@@ -16569,7 +16588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>760</v>
       </c>
@@ -16580,7 +16599,7 @@
         <v>74.985600000000005</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>118</v>
       </c>
@@ -16594,7 +16613,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>120</v>
       </c>
@@ -16608,7 +16627,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>122</v>
       </c>
@@ -16622,7 +16641,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>148</v>
       </c>
@@ -16636,7 +16655,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>152</v>
       </c>
@@ -16650,7 +16669,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>154</v>
       </c>
@@ -16664,7 +16683,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>156</v>
       </c>
@@ -16678,7 +16697,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>182</v>
       </c>
@@ -16692,7 +16711,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>186</v>
       </c>
@@ -16706,7 +16725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>188</v>
       </c>
@@ -16720,7 +16739,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>190</v>
       </c>
@@ -16734,7 +16753,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>760</v>
       </c>
@@ -16745,7 +16764,7 @@
         <v>74.984499999999997</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>446</v>
       </c>
@@ -16759,7 +16778,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>462</v>
       </c>
@@ -16773,7 +16792,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>478</v>
       </c>
@@ -16787,7 +16806,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>494</v>
       </c>
@@ -16801,7 +16820,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>510</v>
       </c>
@@ -16815,7 +16834,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>430</v>
       </c>
@@ -16829,7 +16848,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>447</v>
       </c>
@@ -16843,7 +16862,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>463</v>
       </c>
@@ -16857,7 +16876,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>479</v>
       </c>
@@ -16871,7 +16890,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>495</v>
       </c>
@@ -16885,7 +16904,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>511</v>
       </c>
@@ -16899,7 +16918,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>431</v>
       </c>
@@ -16913,7 +16932,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>448</v>
       </c>
@@ -16927,7 +16946,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>464</v>
       </c>
@@ -16941,7 +16960,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>480</v>
       </c>
@@ -16955,7 +16974,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>496</v>
       </c>
@@ -16969,7 +16988,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>512</v>
       </c>
@@ -16983,7 +17002,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>432</v>
       </c>
@@ -16997,7 +17016,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>449</v>
       </c>
@@ -17011,7 +17030,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>465</v>
       </c>
@@ -17025,7 +17044,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>481</v>
       </c>
@@ -17039,7 +17058,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>497</v>
       </c>
@@ -17053,7 +17072,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>513</v>
       </c>
@@ -17067,7 +17086,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>534</v>
       </c>
@@ -17081,7 +17100,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>536</v>
       </c>
@@ -17095,7 +17114,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>227</v>
       </c>
@@ -17109,7 +17128,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>277</v>
       </c>
@@ -17123,7 +17142,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>229</v>
       </c>
@@ -17137,7 +17156,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>230</v>
       </c>
@@ -17151,7 +17170,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>279</v>
       </c>
@@ -17165,7 +17184,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>231</v>
       </c>
@@ -17179,7 +17198,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>280</v>
       </c>
@@ -17193,7 +17212,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>245</v>
       </c>
@@ -17207,7 +17226,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>293</v>
       </c>
@@ -17221,7 +17240,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>294</v>
       </c>
@@ -17235,7 +17254,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>247</v>
       </c>
@@ -17249,7 +17268,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>295</v>
       </c>
@@ -17263,7 +17282,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>296</v>
       </c>
@@ -17277,7 +17296,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>760</v>
       </c>
@@ -17288,7 +17307,7 @@
         <v>74.977800000000002</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>261</v>
       </c>
@@ -17302,7 +17321,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>309</v>
       </c>
@@ -17316,7 +17335,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>262</v>
       </c>
@@ -17330,7 +17349,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>310</v>
       </c>
@@ -17344,7 +17363,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>263</v>
       </c>
@@ -17358,7 +17377,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>311</v>
       </c>
@@ -17372,7 +17391,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>264</v>
       </c>
@@ -17386,7 +17405,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>312</v>
       </c>
@@ -17400,7 +17419,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>760</v>
       </c>
@@ -17411,7 +17430,7 @@
         <v>74.981200000000001</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>524</v>
       </c>
@@ -17425,7 +17444,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>526</v>
       </c>
@@ -17439,7 +17458,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>527</v>
       </c>
@@ -17453,7 +17472,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>528</v>
       </c>
@@ -17467,7 +17486,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>28</v>
       </c>
@@ -17478,7 +17497,7 @@
         <v>13.6623</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>221</v>
       </c>
@@ -17489,7 +17508,7 @@
         <v>11.9528</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>523</v>
       </c>
@@ -17500,7 +17519,7 @@
         <v>11.689299999999999</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>17</v>
       </c>
@@ -17511,7 +17530,7 @@
         <v>10.5501</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>336</v>
       </c>
@@ -17522,7 +17541,7 @@
         <v>12.6976</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>248</v>
       </c>
@@ -17533,7 +17552,7 @@
         <v>10.746499999999999</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>760</v>
       </c>
@@ -17544,7 +17563,7 @@
         <v>74.981499999999997</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>428</v>
       </c>
@@ -17555,7 +17574,7 @@
         <v>7.6966000000000001</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>709</v>
       </c>
@@ -17566,7 +17585,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>425</v>
       </c>
@@ -17577,7 +17596,7 @@
         <v>9.0972000000000008</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>763</v>
       </c>
@@ -17588,7 +17607,7 @@
         <v>5.1988000000000003</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>760</v>
       </c>
@@ -17599,7 +17618,7 @@
         <v>74.992500000000007</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>328</v>
       </c>
@@ -17613,7 +17632,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>346</v>
       </c>
@@ -17627,7 +17646,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>362</v>
       </c>
@@ -17641,7 +17660,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>378</v>
       </c>
@@ -17655,7 +17674,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>394</v>
       </c>
@@ -17669,7 +17688,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>410</v>
       </c>
@@ -17683,7 +17702,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>330</v>
       </c>
@@ -17697,7 +17716,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>347</v>
       </c>
@@ -17711,7 +17730,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>363</v>
       </c>
@@ -17725,7 +17744,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>379</v>
       </c>
@@ -17739,7 +17758,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>395</v>
       </c>
@@ -17753,7 +17772,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>411</v>
       </c>
@@ -17767,7 +17786,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>331</v>
       </c>
@@ -17781,7 +17800,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>348</v>
       </c>
@@ -17795,7 +17814,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>364</v>
       </c>
@@ -17809,7 +17828,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>380</v>
       </c>
@@ -17823,7 +17842,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>760</v>
       </c>
@@ -17834,7 +17853,7 @@
         <v>74.986800000000002</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>396</v>
       </c>
@@ -17848,7 +17867,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>412</v>
       </c>
@@ -17862,7 +17881,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>332</v>
       </c>
@@ -17876,7 +17895,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>349</v>
       </c>
@@ -17890,7 +17909,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>365</v>
       </c>
@@ -17904,7 +17923,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>381</v>
       </c>
@@ -17918,7 +17937,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>397</v>
       </c>
@@ -17932,7 +17951,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>413</v>
       </c>
@@ -17946,7 +17965,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>711</v>
       </c>
@@ -17960,7 +17979,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>712</v>
       </c>
@@ -17974,7 +17993,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>713</v>
       </c>
@@ -17988,7 +18007,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>760</v>
       </c>
@@ -17997,6 +18016,533 @@
       </c>
       <c r="C154">
         <v>74.956400000000002</v>
+      </c>
+      <c r="F154" s="1"/>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>760</v>
+      </c>
+      <c r="B155">
+        <v>24</v>
+      </c>
+      <c r="C155">
+        <v>74.961699999999993</v>
+      </c>
+      <c r="F155" s="1"/>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>108</v>
+      </c>
+      <c r="B156">
+        <v>24</v>
+      </c>
+      <c r="C156">
+        <v>20.435700000000001</v>
+      </c>
+      <c r="F156" s="1"/>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A157" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B157">
+        <v>24</v>
+      </c>
+      <c r="C157">
+        <v>10.076000000000001</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F157" s="1"/>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A158" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B158">
+        <v>24</v>
+      </c>
+      <c r="C158">
+        <v>13.6595</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F158" s="1"/>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A159" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B159">
+        <v>24</v>
+      </c>
+      <c r="C159">
+        <v>8.1547999999999998</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F159" s="1"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A160" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="B160">
+        <v>24</v>
+      </c>
+      <c r="C160">
+        <v>11.1936</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="F160" s="1"/>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A161" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="B161">
+        <v>23.9</v>
+      </c>
+      <c r="C161">
+        <v>8.8575999999999997</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F161" s="1"/>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B162">
+        <v>23.9</v>
+      </c>
+      <c r="C162">
+        <v>74.983699999999999</v>
+      </c>
+      <c r="F162" s="1"/>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="B163">
+        <v>23.9</v>
+      </c>
+      <c r="C163">
+        <v>11.9217</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F163" s="1"/>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A164" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B164">
+        <v>23.9</v>
+      </c>
+      <c r="C164">
+        <v>14.3188</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F164" s="1"/>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A165" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B165">
+        <v>23.9</v>
+      </c>
+      <c r="C165">
+        <v>11.4803</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="F165" s="1"/>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A166" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B166">
+        <v>23.9</v>
+      </c>
+      <c r="C166">
+        <v>12.7316</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="F166" s="1"/>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A167" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B167">
+        <v>24.1</v>
+      </c>
+      <c r="C167">
+        <v>74.984099999999998</v>
+      </c>
+      <c r="F167" s="1"/>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A168" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B168">
+        <v>24.1</v>
+      </c>
+      <c r="C168">
+        <v>8.6835000000000004</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="F168" s="1"/>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A169" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B169">
+        <v>24.1</v>
+      </c>
+      <c r="C169">
+        <v>10.024699999999999</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="F169" s="1"/>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A170" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B170">
+        <v>24.1</v>
+      </c>
+      <c r="C170">
+        <v>12.001799999999999</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="F170" s="1"/>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A171" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B171">
+        <v>24</v>
+      </c>
+      <c r="C171">
+        <v>74.984300000000005</v>
+      </c>
+      <c r="F171" s="1"/>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A172" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B172">
+        <v>24</v>
+      </c>
+      <c r="C172">
+        <v>15.422599999999999</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="F172" s="1"/>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A173" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B173">
+        <v>24</v>
+      </c>
+      <c r="C173">
+        <v>11.7668</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="F173" s="1"/>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A174" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B174">
+        <v>24</v>
+      </c>
+      <c r="C174">
+        <v>5.9949000000000003</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F174" s="1"/>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A175" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B175">
+        <v>24</v>
+      </c>
+      <c r="C175">
+        <v>17.051500000000001</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="F175" s="1"/>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A176" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B176">
+        <v>24</v>
+      </c>
+      <c r="C176">
+        <v>6.0857999999999999</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F176" s="1"/>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A177" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B177">
+        <v>24</v>
+      </c>
+      <c r="C177">
+        <v>7.6868999999999996</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F177" s="1"/>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A178" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B178">
+        <v>24</v>
+      </c>
+      <c r="C178">
+        <v>10.0076</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="F178" s="1"/>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A179" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B179">
+        <v>24</v>
+      </c>
+      <c r="C179">
+        <v>6.6196000000000002</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="F179" s="1"/>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A180" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B180">
+        <v>24</v>
+      </c>
+      <c r="C180">
+        <v>9.4603000000000002</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F180" s="1"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A181" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B181">
+        <v>24</v>
+      </c>
+      <c r="C181">
+        <v>7.4116999999999997</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="F181" s="1"/>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A182" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B182">
+        <v>23.9</v>
+      </c>
+      <c r="C182">
+        <v>7.9580000000000002</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F182" s="1"/>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A183" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B183">
+        <v>23.9</v>
+      </c>
+      <c r="C183">
+        <v>74.982600000000005</v>
+      </c>
+      <c r="F183" s="1"/>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A184" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B184">
+        <v>23.9</v>
+      </c>
+      <c r="C184">
+        <v>9.5602999999999998</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A185" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B185">
+        <v>23.9</v>
+      </c>
+      <c r="C185">
+        <v>10.0602</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A186" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B186">
+        <v>23.9</v>
+      </c>
+      <c r="C186">
+        <v>8.2233999999999998</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A187" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B187">
+        <v>24.1</v>
+      </c>
+      <c r="C187">
+        <v>6.0327000000000002</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A188" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B188">
+        <v>24.1</v>
+      </c>
+      <c r="C188">
+        <v>7.9481000000000002</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A189" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B189">
+        <v>24.1</v>
+      </c>
+      <c r="C189">
+        <v>9.4989000000000008</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A190" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B190">
+        <v>24.1</v>
+      </c>
+      <c r="C190">
+        <v>7.6905000000000001</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A191" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B191">
+        <v>24.1</v>
+      </c>
+      <c r="C191">
+        <v>74.982500000000002</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Final_BW.xlsx
+++ b/Data/Final_BW.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Donahue Lab\Desktop\GitHub\biofac\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A562B3-7CAB-477A-B785-C84AA417F3B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F3E5D4-4275-4984-82B1-EB660B600812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="BW" sheetId="2" r:id="rId2"/>
+    <sheet name="Frag checklist" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$577</definedName>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4066" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4975" uniqueCount="776">
   <si>
     <t>sample_ID</t>
   </si>
@@ -2345,6 +2346,18 @@
   </si>
   <si>
     <t>A18_1_3SP</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>respo 1, don't think label is right</t>
+  </si>
+  <si>
+    <t>Labeled tank 11 in respo?</t>
   </si>
 </sst>
 </file>
@@ -2372,12 +2385,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2392,10 +2411,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15966,7 +15986,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D93EAE40-CB66-4677-8B60-FAEB87FECE43}">
-  <dimension ref="A1:F321"/>
+  <dimension ref="A1:F306"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
@@ -16451,13 +16471,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B29">
         <v>24</v>
       </c>
       <c r="C29">
-        <v>7.3033999999999999</v>
+        <v>14.323600000000001</v>
       </c>
       <c r="D29" t="s">
         <v>12</v>
@@ -16468,13 +16488,13 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B30">
         <v>24</v>
       </c>
       <c r="C30">
-        <v>14.323600000000001</v>
+        <v>9.5045000000000002</v>
       </c>
       <c r="D30" t="s">
         <v>12</v>
@@ -16485,13 +16505,13 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="B31">
         <v>24</v>
       </c>
       <c r="C31">
-        <v>9.5045000000000002</v>
+        <v>21.1389</v>
       </c>
       <c r="D31" t="s">
         <v>12</v>
@@ -16502,13 +16522,13 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B32">
         <v>24</v>
       </c>
       <c r="C32">
-        <v>21.1389</v>
+        <v>13.4053</v>
       </c>
       <c r="D32" t="s">
         <v>12</v>
@@ -16519,13 +16539,13 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B33">
         <v>24</v>
       </c>
       <c r="C33">
-        <v>13.4053</v>
+        <v>11.270799999999999</v>
       </c>
       <c r="D33" t="s">
         <v>12</v>
@@ -16536,13 +16556,13 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B34">
         <v>24</v>
       </c>
       <c r="C34">
-        <v>11.270799999999999</v>
+        <v>13.087300000000001</v>
       </c>
       <c r="D34" t="s">
         <v>12</v>
@@ -16553,13 +16573,13 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="B35">
         <v>24</v>
       </c>
       <c r="C35">
-        <v>13.087300000000001</v>
+        <v>23.3123</v>
       </c>
       <c r="D35" t="s">
         <v>12</v>
@@ -16570,16 +16590,13 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>114</v>
+        <v>760</v>
       </c>
       <c r="B36">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C36">
-        <v>23.3123</v>
-      </c>
-      <c r="D36" t="s">
-        <v>12</v>
+        <v>74.985600000000005</v>
       </c>
       <c r="E36" s="2">
         <v>46140</v>
@@ -16587,13 +16604,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>760</v>
+        <v>118</v>
       </c>
       <c r="B37">
         <v>24.1</v>
       </c>
       <c r="C37">
-        <v>74.985600000000005</v>
+        <v>17.591999999999999</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
       </c>
       <c r="E37" s="2">
         <v>46140</v>
@@ -16601,13 +16621,13 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B38">
         <v>24.1</v>
       </c>
       <c r="C38">
-        <v>17.591999999999999</v>
+        <v>21.884799999999998</v>
       </c>
       <c r="D38" t="s">
         <v>12</v>
@@ -16618,13 +16638,13 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B39">
         <v>24.1</v>
       </c>
       <c r="C39">
-        <v>21.884799999999998</v>
+        <v>10.5223</v>
       </c>
       <c r="D39" t="s">
         <v>12</v>
@@ -16635,13 +16655,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="B40">
         <v>24.1</v>
       </c>
       <c r="C40">
-        <v>10.5223</v>
+        <v>6.0967000000000002</v>
       </c>
       <c r="D40" t="s">
         <v>12</v>
@@ -16652,13 +16672,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B41">
         <v>24.1</v>
       </c>
       <c r="C41">
-        <v>6.0967000000000002</v>
+        <v>6.9638999999999998</v>
       </c>
       <c r="D41" t="s">
         <v>12</v>
@@ -16669,13 +16689,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B42">
         <v>24.1</v>
       </c>
       <c r="C42">
-        <v>6.9638999999999998</v>
+        <v>9.8557000000000006</v>
       </c>
       <c r="D42" t="s">
         <v>12</v>
@@ -16686,13 +16706,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B43">
         <v>24.1</v>
       </c>
       <c r="C43">
-        <v>9.8557000000000006</v>
+        <v>6.2967000000000004</v>
       </c>
       <c r="D43" t="s">
         <v>12</v>
@@ -16703,13 +16723,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="B44">
         <v>24.1</v>
       </c>
       <c r="C44">
-        <v>6.2967000000000004</v>
+        <v>22.4466</v>
       </c>
       <c r="D44" t="s">
         <v>12</v>
@@ -16720,13 +16740,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B45">
         <v>24.1</v>
       </c>
       <c r="C45">
-        <v>22.4466</v>
+        <v>21.2606</v>
       </c>
       <c r="D45" t="s">
         <v>12</v>
@@ -16737,13 +16757,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B46">
         <v>24.1</v>
       </c>
       <c r="C46">
-        <v>21.2606</v>
+        <v>28.217700000000001</v>
       </c>
       <c r="D46" t="s">
         <v>12</v>
@@ -16754,13 +16774,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B47">
         <v>24.1</v>
       </c>
       <c r="C47">
-        <v>28.217700000000001</v>
+        <v>22.2225</v>
       </c>
       <c r="D47" t="s">
         <v>12</v>
@@ -16771,16 +16791,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>190</v>
+        <v>760</v>
       </c>
       <c r="B48">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C48">
-        <v>22.2225</v>
-      </c>
-      <c r="D48" t="s">
-        <v>12</v>
+        <v>74.984499999999997</v>
       </c>
       <c r="E48" s="2">
         <v>46140</v>
@@ -16788,13 +16805,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>760</v>
+        <v>446</v>
       </c>
       <c r="B49">
         <v>24</v>
       </c>
       <c r="C49">
-        <v>74.984499999999997</v>
+        <v>5.1662999999999997</v>
+      </c>
+      <c r="D49" t="s">
+        <v>329</v>
       </c>
       <c r="E49" s="2">
         <v>46140</v>
@@ -16802,13 +16822,13 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="B50">
         <v>24</v>
       </c>
       <c r="C50">
-        <v>5.1662999999999997</v>
+        <v>7.3392999999999997</v>
       </c>
       <c r="D50" t="s">
         <v>329</v>
@@ -16819,13 +16839,13 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="B51">
         <v>24</v>
       </c>
       <c r="C51">
-        <v>7.3392999999999997</v>
+        <v>9.2127999999999997</v>
       </c>
       <c r="D51" t="s">
         <v>329</v>
@@ -16836,13 +16856,13 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="B52">
         <v>24</v>
       </c>
       <c r="C52">
-        <v>9.2127999999999997</v>
+        <v>7.2032999999999996</v>
       </c>
       <c r="D52" t="s">
         <v>329</v>
@@ -16853,13 +16873,13 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>494</v>
+        <v>510</v>
       </c>
       <c r="B53">
         <v>24</v>
       </c>
       <c r="C53">
-        <v>7.2032999999999996</v>
+        <v>6.1230000000000002</v>
       </c>
       <c r="D53" t="s">
         <v>329</v>
@@ -16870,13 +16890,13 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>510</v>
+        <v>430</v>
       </c>
       <c r="B54">
         <v>24</v>
       </c>
       <c r="C54">
-        <v>6.1230000000000002</v>
+        <v>9.6420999999999992</v>
       </c>
       <c r="D54" t="s">
         <v>329</v>
@@ -16887,13 +16907,13 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="B55">
         <v>24</v>
       </c>
       <c r="C55">
-        <v>9.6420999999999992</v>
+        <v>7.1683000000000003</v>
       </c>
       <c r="D55" t="s">
         <v>329</v>
@@ -16904,13 +16924,13 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="B56">
         <v>24</v>
       </c>
       <c r="C56">
-        <v>7.1683000000000003</v>
+        <v>8.6335999999999995</v>
       </c>
       <c r="D56" t="s">
         <v>329</v>
@@ -16921,13 +16941,13 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="B57">
         <v>24</v>
       </c>
       <c r="C57">
-        <v>8.6335999999999995</v>
+        <v>6.1786000000000003</v>
       </c>
       <c r="D57" t="s">
         <v>329</v>
@@ -16938,13 +16958,13 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="B58">
         <v>24</v>
       </c>
       <c r="C58">
-        <v>6.1786000000000003</v>
+        <v>6.1332000000000004</v>
       </c>
       <c r="D58" t="s">
         <v>329</v>
@@ -16955,13 +16975,13 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>495</v>
+        <v>511</v>
       </c>
       <c r="B59">
         <v>24</v>
       </c>
       <c r="C59">
-        <v>6.1332000000000004</v>
+        <v>6.4919000000000002</v>
       </c>
       <c r="D59" t="s">
         <v>329</v>
@@ -16972,13 +16992,13 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>511</v>
+        <v>431</v>
       </c>
       <c r="B60">
         <v>24</v>
       </c>
       <c r="C60">
-        <v>6.4919000000000002</v>
+        <v>6.4764999999999997</v>
       </c>
       <c r="D60" t="s">
         <v>329</v>
@@ -16989,13 +17009,13 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
       <c r="B61">
         <v>24</v>
       </c>
       <c r="C61">
-        <v>6.4764999999999997</v>
+        <v>6.0129000000000001</v>
       </c>
       <c r="D61" t="s">
         <v>329</v>
@@ -17006,13 +17026,13 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="B62">
         <v>24</v>
       </c>
       <c r="C62">
-        <v>6.0129000000000001</v>
+        <v>5.5041000000000002</v>
       </c>
       <c r="D62" t="s">
         <v>329</v>
@@ -17023,13 +17043,13 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>464</v>
+        <v>480</v>
       </c>
       <c r="B63">
         <v>24</v>
       </c>
       <c r="C63">
-        <v>5.5041000000000002</v>
+        <v>5.1725000000000003</v>
       </c>
       <c r="D63" t="s">
         <v>329</v>
@@ -17040,13 +17060,13 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="B64">
         <v>24</v>
       </c>
       <c r="C64">
-        <v>5.1725000000000003</v>
+        <v>8.7187999999999999</v>
       </c>
       <c r="D64" t="s">
         <v>329</v>
@@ -17057,13 +17077,13 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>496</v>
+        <v>512</v>
       </c>
       <c r="B65">
         <v>24</v>
       </c>
       <c r="C65">
-        <v>8.7187999999999999</v>
+        <v>7.6140999999999996</v>
       </c>
       <c r="D65" t="s">
         <v>329</v>
@@ -17074,13 +17094,13 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>512</v>
+        <v>432</v>
       </c>
       <c r="B66">
         <v>24</v>
       </c>
       <c r="C66">
-        <v>7.6140999999999996</v>
+        <v>9.4806000000000008</v>
       </c>
       <c r="D66" t="s">
         <v>329</v>
@@ -17091,13 +17111,13 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="B67">
         <v>24</v>
       </c>
       <c r="C67">
-        <v>9.4806000000000008</v>
+        <v>5.5156999999999998</v>
       </c>
       <c r="D67" t="s">
         <v>329</v>
@@ -17108,13 +17128,13 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="B68">
         <v>24</v>
       </c>
       <c r="C68">
-        <v>5.5156999999999998</v>
+        <v>5.3971</v>
       </c>
       <c r="D68" t="s">
         <v>329</v>
@@ -17125,13 +17145,13 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="B69">
         <v>24</v>
       </c>
       <c r="C69">
-        <v>5.3971</v>
+        <v>6.8205999999999998</v>
       </c>
       <c r="D69" t="s">
         <v>329</v>
@@ -17142,13 +17162,13 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>481</v>
+        <v>497</v>
       </c>
       <c r="B70">
         <v>24</v>
       </c>
       <c r="C70">
-        <v>6.8205999999999998</v>
+        <v>10.0418</v>
       </c>
       <c r="D70" t="s">
         <v>329</v>
@@ -17159,13 +17179,13 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>497</v>
+        <v>513</v>
       </c>
       <c r="B71">
         <v>24</v>
       </c>
       <c r="C71">
-        <v>10.0418</v>
+        <v>5.7984999999999998</v>
       </c>
       <c r="D71" t="s">
         <v>329</v>
@@ -17176,16 +17196,16 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>513</v>
+        <v>536</v>
       </c>
       <c r="B72">
         <v>24</v>
       </c>
       <c r="C72">
-        <v>5.7984999999999998</v>
+        <v>13.723000000000001</v>
       </c>
       <c r="D72" t="s">
-        <v>329</v>
+        <v>720</v>
       </c>
       <c r="E72" s="2">
         <v>46140</v>
@@ -17193,16 +17213,16 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>534</v>
+        <v>277</v>
       </c>
       <c r="B73">
         <v>24</v>
       </c>
       <c r="C73">
-        <v>9.4158000000000008</v>
+        <v>7.7462999999999997</v>
       </c>
       <c r="D73" t="s">
-        <v>720</v>
+        <v>228</v>
       </c>
       <c r="E73" s="2">
         <v>46140</v>
@@ -17210,16 +17230,16 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>536</v>
+        <v>229</v>
       </c>
       <c r="B74">
         <v>24</v>
       </c>
       <c r="C74">
-        <v>13.723000000000001</v>
+        <v>7.8865999999999996</v>
       </c>
       <c r="D74" t="s">
-        <v>720</v>
+        <v>228</v>
       </c>
       <c r="E74" s="2">
         <v>46140</v>
@@ -17227,13 +17247,13 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
       <c r="B75">
         <v>24</v>
       </c>
       <c r="C75">
-        <v>10.4968</v>
+        <v>11.303800000000001</v>
       </c>
       <c r="D75" t="s">
         <v>228</v>
@@ -17244,13 +17264,13 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>277</v>
+        <v>231</v>
       </c>
       <c r="B76">
         <v>24</v>
       </c>
       <c r="C76">
-        <v>7.7462999999999997</v>
+        <v>7.6952999999999996</v>
       </c>
       <c r="D76" t="s">
         <v>228</v>
@@ -17261,13 +17281,13 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>229</v>
+        <v>280</v>
       </c>
       <c r="B77">
         <v>24</v>
       </c>
       <c r="C77">
-        <v>7.8865999999999996</v>
+        <v>8.9859000000000009</v>
       </c>
       <c r="D77" t="s">
         <v>228</v>
@@ -17278,13 +17298,13 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="B78">
         <v>24</v>
       </c>
       <c r="C78">
-        <v>10.754300000000001</v>
+        <v>11.486000000000001</v>
       </c>
       <c r="D78" t="s">
         <v>228</v>
@@ -17295,13 +17315,13 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="B79">
         <v>24</v>
       </c>
       <c r="C79">
-        <v>11.303800000000001</v>
+        <v>10.836499999999999</v>
       </c>
       <c r="D79" t="s">
         <v>228</v>
@@ -17312,13 +17332,13 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>231</v>
+        <v>294</v>
       </c>
       <c r="B80">
         <v>24</v>
       </c>
       <c r="C80">
-        <v>7.6952999999999996</v>
+        <v>5.3514999999999997</v>
       </c>
       <c r="D80" t="s">
         <v>228</v>
@@ -17329,13 +17349,13 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>280</v>
+        <v>247</v>
       </c>
       <c r="B81">
         <v>24</v>
       </c>
       <c r="C81">
-        <v>8.9859000000000009</v>
+        <v>7.9664999999999999</v>
       </c>
       <c r="D81" t="s">
         <v>228</v>
@@ -17346,13 +17366,13 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>245</v>
+        <v>295</v>
       </c>
       <c r="B82">
         <v>24</v>
       </c>
       <c r="C82">
-        <v>11.486000000000001</v>
+        <v>6.4123999999999999</v>
       </c>
       <c r="D82" t="s">
         <v>228</v>
@@ -17363,13 +17383,13 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B83">
         <v>24</v>
       </c>
       <c r="C83">
-        <v>10.836499999999999</v>
+        <v>9.0233000000000008</v>
       </c>
       <c r="D83" t="s">
         <v>228</v>
@@ -17380,16 +17400,13 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>294</v>
+        <v>760</v>
       </c>
       <c r="B84">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C84">
-        <v>5.3514999999999997</v>
-      </c>
-      <c r="D84" t="s">
-        <v>228</v>
+        <v>74.977800000000002</v>
       </c>
       <c r="E84" s="2">
         <v>46140</v>
@@ -17397,13 +17414,13 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="B85">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C85">
-        <v>7.9664999999999999</v>
+        <v>15.9406</v>
       </c>
       <c r="D85" t="s">
         <v>228</v>
@@ -17414,13 +17431,13 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B86">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C86">
-        <v>6.4123999999999999</v>
+        <v>18.651299999999999</v>
       </c>
       <c r="D86" t="s">
         <v>228</v>
@@ -17431,13 +17448,13 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>296</v>
+        <v>262</v>
       </c>
       <c r="B87">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C87">
-        <v>9.0233000000000008</v>
+        <v>18.712399999999999</v>
       </c>
       <c r="D87" t="s">
         <v>228</v>
@@ -17448,13 +17465,16 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>760</v>
+        <v>310</v>
       </c>
       <c r="B88">
         <v>24.1</v>
       </c>
       <c r="C88">
-        <v>74.977800000000002</v>
+        <v>25.058299999999999</v>
+      </c>
+      <c r="D88" t="s">
+        <v>228</v>
       </c>
       <c r="E88" s="2">
         <v>46140</v>
@@ -17462,13 +17482,13 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B89">
         <v>24.1</v>
       </c>
       <c r="C89">
-        <v>15.9406</v>
+        <v>17.875</v>
       </c>
       <c r="D89" t="s">
         <v>228</v>
@@ -17479,13 +17499,13 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B90">
         <v>24.1</v>
       </c>
       <c r="C90">
-        <v>18.651299999999999</v>
+        <v>15.45</v>
       </c>
       <c r="D90" t="s">
         <v>228</v>
@@ -17496,13 +17516,13 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B91">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C91">
-        <v>18.712399999999999</v>
+        <v>13.537100000000001</v>
       </c>
       <c r="D91" t="s">
         <v>228</v>
@@ -17513,13 +17533,13 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B92">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C92">
-        <v>25.058299999999999</v>
+        <v>12.5085</v>
       </c>
       <c r="D92" t="s">
         <v>228</v>
@@ -17530,16 +17550,13 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>263</v>
+        <v>760</v>
       </c>
       <c r="B93">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C93">
-        <v>17.875</v>
-      </c>
-      <c r="D93" t="s">
-        <v>228</v>
+        <v>74.981200000000001</v>
       </c>
       <c r="E93" s="2">
         <v>46140</v>
@@ -17547,16 +17564,16 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>311</v>
+        <v>524</v>
       </c>
       <c r="B94">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C94">
-        <v>15.45</v>
+        <v>12.9214</v>
       </c>
       <c r="D94" t="s">
-        <v>228</v>
+        <v>525</v>
       </c>
       <c r="E94" s="2">
         <v>46140</v>
@@ -17564,16 +17581,16 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>264</v>
+        <v>526</v>
       </c>
       <c r="B95">
         <v>24</v>
       </c>
       <c r="C95">
-        <v>13.537100000000001</v>
+        <v>13.1183</v>
       </c>
       <c r="D95" t="s">
-        <v>228</v>
+        <v>525</v>
       </c>
       <c r="E95" s="2">
         <v>46140</v>
@@ -17581,252 +17598,282 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>312</v>
+        <v>527</v>
       </c>
       <c r="B96">
         <v>24</v>
       </c>
       <c r="C96">
-        <v>12.5085</v>
+        <v>8.4278999999999993</v>
       </c>
       <c r="D96" t="s">
-        <v>228</v>
+        <v>525</v>
       </c>
       <c r="E96" s="2">
         <v>46140</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>760</v>
+        <v>528</v>
       </c>
       <c r="B97">
         <v>24</v>
       </c>
       <c r="C97">
-        <v>74.981200000000001</v>
+        <v>6.9798</v>
+      </c>
+      <c r="D97" t="s">
+        <v>525</v>
       </c>
       <c r="E97" s="2">
         <v>46140</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>524</v>
+        <v>28</v>
       </c>
       <c r="B98">
         <v>24</v>
       </c>
       <c r="C98">
-        <v>12.9214</v>
+        <v>13.6623</v>
       </c>
       <c r="D98" t="s">
-        <v>525</v>
+        <v>30</v>
       </c>
       <c r="E98" s="2">
         <v>46140</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>526</v>
+        <v>17</v>
       </c>
       <c r="B99">
         <v>24</v>
       </c>
       <c r="C99">
-        <v>13.1183</v>
+        <v>10.5501</v>
       </c>
       <c r="D99" t="s">
-        <v>525</v>
+        <v>12</v>
       </c>
       <c r="E99" s="2">
         <v>46140</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>527</v>
+        <v>336</v>
       </c>
       <c r="B100">
         <v>24</v>
       </c>
       <c r="C100">
-        <v>8.4278999999999993</v>
+        <v>12.6976</v>
       </c>
       <c r="D100" t="s">
-        <v>525</v>
+        <v>334</v>
       </c>
       <c r="E100" s="2">
         <v>46140</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>528</v>
+        <v>248</v>
       </c>
       <c r="B101">
         <v>24</v>
       </c>
       <c r="C101">
-        <v>6.9798</v>
+        <v>10.746499999999999</v>
       </c>
       <c r="D101" t="s">
-        <v>525</v>
+        <v>228</v>
       </c>
       <c r="E101" s="2">
         <v>46140</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>28</v>
+        <v>760</v>
       </c>
       <c r="B102">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C102">
-        <v>13.6623</v>
+        <v>74.981499999999997</v>
       </c>
       <c r="E102" s="2">
         <v>46140</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>221</v>
+        <v>428</v>
       </c>
       <c r="B103">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C103">
-        <v>11.9528</v>
+        <v>7.6966000000000001</v>
+      </c>
+      <c r="D103" t="s">
+        <v>329</v>
       </c>
       <c r="E103" s="2">
         <v>46140</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>523</v>
+        <v>709</v>
       </c>
       <c r="B104">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C104">
-        <v>11.689299999999999</v>
+        <v>14.1</v>
+      </c>
+      <c r="D104" t="s">
+        <v>710</v>
       </c>
       <c r="E104" s="2">
         <v>46140</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>17</v>
+        <v>425</v>
       </c>
       <c r="B105">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C105">
-        <v>10.5501</v>
+        <v>9.0972000000000008</v>
+      </c>
+      <c r="D105" t="s">
+        <v>424</v>
       </c>
       <c r="E105" s="2">
         <v>46140</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>336</v>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="3" t="s">
+        <v>763</v>
       </c>
       <c r="B106">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C106">
-        <v>12.6976</v>
+        <v>5.1988000000000003</v>
       </c>
       <c r="E106" s="2">
         <v>46140</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F106" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>248</v>
+        <v>760</v>
       </c>
       <c r="B107">
         <v>24</v>
       </c>
       <c r="C107">
-        <v>10.746499999999999</v>
+        <v>74.992500000000007</v>
       </c>
       <c r="E107" s="2">
         <v>46140</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>760</v>
+        <v>328</v>
       </c>
       <c r="B108">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C108">
-        <v>74.981499999999997</v>
+        <v>10.2178</v>
+      </c>
+      <c r="D108" t="s">
+        <v>429</v>
       </c>
       <c r="E108" s="2">
         <v>46140</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>428</v>
+        <v>346</v>
       </c>
       <c r="B109">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C109">
-        <v>7.6966000000000001</v>
+        <v>11.0235</v>
+      </c>
+      <c r="D109" t="s">
+        <v>429</v>
       </c>
       <c r="E109" s="2">
         <v>46140</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>709</v>
+        <v>362</v>
       </c>
       <c r="B110">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C110">
-        <v>14.1</v>
+        <v>14.263999999999999</v>
+      </c>
+      <c r="D110" t="s">
+        <v>429</v>
       </c>
       <c r="E110" s="2">
         <v>46140</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>425</v>
+        <v>378</v>
       </c>
       <c r="B111">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C111">
-        <v>9.0972000000000008</v>
+        <v>12.041499999999999</v>
+      </c>
+      <c r="D111" t="s">
+        <v>429</v>
       </c>
       <c r="E111" s="2">
         <v>46140</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>763</v>
+        <v>394</v>
       </c>
       <c r="B112">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C112">
-        <v>5.1988000000000003</v>
+        <v>14.710800000000001</v>
+      </c>
+      <c r="D112" t="s">
+        <v>429</v>
       </c>
       <c r="E112" s="2">
         <v>46140</v>
@@ -17834,13 +17881,16 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>760</v>
+        <v>410</v>
       </c>
       <c r="B113">
         <v>24</v>
       </c>
       <c r="C113">
-        <v>74.992500000000007</v>
+        <v>8.5482999999999993</v>
+      </c>
+      <c r="D113" t="s">
+        <v>429</v>
       </c>
       <c r="E113" s="2">
         <v>46140</v>
@@ -17848,13 +17898,13 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B114">
         <v>24</v>
       </c>
       <c r="C114">
-        <v>10.2178</v>
+        <v>11.259</v>
       </c>
       <c r="D114" t="s">
         <v>429</v>
@@ -17865,13 +17915,13 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B115">
         <v>24</v>
       </c>
       <c r="C115">
-        <v>11.0235</v>
+        <v>14.8864</v>
       </c>
       <c r="D115" t="s">
         <v>429</v>
@@ -17882,13 +17932,13 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B116">
         <v>24</v>
       </c>
       <c r="C116">
-        <v>14.263999999999999</v>
+        <v>8.7667999999999999</v>
       </c>
       <c r="D116" t="s">
         <v>429</v>
@@ -17899,13 +17949,13 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B117">
         <v>24</v>
       </c>
       <c r="C117">
-        <v>12.041499999999999</v>
+        <v>9.7637999999999998</v>
       </c>
       <c r="D117" t="s">
         <v>429</v>
@@ -17916,13 +17966,13 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B118">
         <v>24</v>
       </c>
       <c r="C118">
-        <v>14.710800000000001</v>
+        <v>14.6288</v>
       </c>
       <c r="D118" t="s">
         <v>429</v>
@@ -17933,13 +17983,13 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B119">
         <v>24</v>
       </c>
       <c r="C119">
-        <v>8.5482999999999993</v>
+        <v>11.2728</v>
       </c>
       <c r="D119" t="s">
         <v>429</v>
@@ -17950,13 +18000,13 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B120">
         <v>24</v>
       </c>
       <c r="C120">
-        <v>11.259</v>
+        <v>9.4731000000000005</v>
       </c>
       <c r="D120" t="s">
         <v>429</v>
@@ -17967,13 +18017,13 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B121">
         <v>24</v>
       </c>
       <c r="C121">
-        <v>14.8864</v>
+        <v>9.4133999999999993</v>
       </c>
       <c r="D121" t="s">
         <v>429</v>
@@ -17984,13 +18034,13 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B122">
         <v>24</v>
       </c>
       <c r="C122">
-        <v>8.7667999999999999</v>
+        <v>8.0586000000000002</v>
       </c>
       <c r="D122" t="s">
         <v>429</v>
@@ -18001,13 +18051,13 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B123">
         <v>24</v>
       </c>
       <c r="C123">
-        <v>9.7637999999999998</v>
+        <v>13.254099999999999</v>
       </c>
       <c r="D123" t="s">
         <v>429</v>
@@ -18018,16 +18068,13 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>395</v>
+        <v>760</v>
       </c>
       <c r="B124">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C124">
-        <v>14.6288</v>
-      </c>
-      <c r="D124" t="s">
-        <v>429</v>
+        <v>74.986800000000002</v>
       </c>
       <c r="E124" s="2">
         <v>46140</v>
@@ -18035,13 +18082,13 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="B125">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C125">
-        <v>11.2728</v>
+        <v>12.8993</v>
       </c>
       <c r="D125" t="s">
         <v>429</v>
@@ -18052,13 +18099,13 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>331</v>
+        <v>412</v>
       </c>
       <c r="B126">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C126">
-        <v>9.4731000000000005</v>
+        <v>7.5430999999999999</v>
       </c>
       <c r="D126" t="s">
         <v>429</v>
@@ -18069,13 +18116,13 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="B127">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C127">
-        <v>9.4133999999999993</v>
+        <v>9.4292999999999996</v>
       </c>
       <c r="D127" t="s">
         <v>429</v>
@@ -18086,13 +18133,13 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="B128">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C128">
-        <v>8.0586000000000002</v>
+        <v>7.1138000000000003</v>
       </c>
       <c r="D128" t="s">
         <v>429</v>
@@ -18103,13 +18150,13 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="B129">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C129">
-        <v>13.254099999999999</v>
+        <v>8.5813000000000006</v>
       </c>
       <c r="D129" t="s">
         <v>429</v>
@@ -18120,13 +18167,16 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>760</v>
+        <v>381</v>
       </c>
       <c r="B130">
         <v>24.1</v>
       </c>
       <c r="C130">
-        <v>74.986800000000002</v>
+        <v>7.9947999999999997</v>
+      </c>
+      <c r="D130" t="s">
+        <v>429</v>
       </c>
       <c r="E130" s="2">
         <v>46140</v>
@@ -18134,13 +18184,13 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B131">
         <v>24.1</v>
       </c>
       <c r="C131">
-        <v>12.8993</v>
+        <v>11.347799999999999</v>
       </c>
       <c r="D131" t="s">
         <v>429</v>
@@ -18151,13 +18201,13 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B132">
         <v>24.1</v>
       </c>
       <c r="C132">
-        <v>7.5430999999999999</v>
+        <v>10.465299999999999</v>
       </c>
       <c r="D132" t="s">
         <v>429</v>
@@ -18168,166 +18218,166 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>332</v>
+        <v>760</v>
       </c>
       <c r="B133">
         <v>24.1</v>
       </c>
       <c r="C133">
-        <v>9.4292999999999996</v>
-      </c>
-      <c r="D133" t="s">
-        <v>429</v>
+        <v>74.956400000000002</v>
       </c>
       <c r="E133" s="2">
         <v>46140</v>
       </c>
+      <c r="F133" s="1"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>349</v>
+        <v>760</v>
       </c>
       <c r="B134">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C134">
-        <v>7.1138000000000003</v>
-      </c>
-      <c r="D134" t="s">
-        <v>429</v>
+        <v>74.961699999999993</v>
       </c>
       <c r="E134" s="2">
         <v>46140</v>
       </c>
+      <c r="F134" s="1"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>365</v>
+        <v>108</v>
       </c>
       <c r="B135">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C135">
-        <v>8.5813000000000006</v>
-      </c>
-      <c r="D135" t="s">
-        <v>429</v>
+        <v>20.435700000000001</v>
       </c>
       <c r="E135" s="2">
         <v>46140</v>
       </c>
+      <c r="F135" s="1"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
-        <v>381</v>
+      <c r="A136" s="1" t="s">
+        <v>229</v>
       </c>
       <c r="B136">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C136">
-        <v>7.9947999999999997</v>
-      </c>
-      <c r="D136" t="s">
-        <v>429</v>
+        <v>10.076000000000001</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>228</v>
       </c>
       <c r="E136" s="2">
         <v>46140</v>
       </c>
+      <c r="F136" s="1"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>397</v>
+      <c r="A137" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="B137">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C137">
-        <v>11.347799999999999</v>
-      </c>
-      <c r="D137" t="s">
-        <v>429</v>
+        <v>13.6595</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="E137" s="2">
         <v>46140</v>
       </c>
+      <c r="F137" s="1"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>413</v>
+      <c r="A138" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="B138">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C138">
-        <v>10.465299999999999</v>
-      </c>
-      <c r="D138" t="s">
-        <v>429</v>
+        <v>8.1547999999999998</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="E138" s="2">
         <v>46140</v>
       </c>
+      <c r="F138" s="1"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
-        <v>711</v>
+      <c r="A139" s="1" t="s">
+        <v>537</v>
       </c>
       <c r="B139">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C139">
-        <v>13.527799999999999</v>
-      </c>
-      <c r="D139" t="s">
-        <v>710</v>
+        <v>11.1936</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>720</v>
       </c>
       <c r="E139" s="2">
         <v>46140</v>
       </c>
+      <c r="F139" s="1"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>712</v>
+      <c r="A140" s="1" t="s">
+        <v>764</v>
       </c>
       <c r="B140">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="C140">
-        <v>7.5054999999999996</v>
-      </c>
-      <c r="D140" t="s">
-        <v>710</v>
+        <v>8.8575999999999997</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>233</v>
       </c>
       <c r="E140" s="2">
         <v>46140</v>
       </c>
+      <c r="F140" s="1"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
-        <v>713</v>
+      <c r="A141" s="1" t="s">
+        <v>760</v>
       </c>
       <c r="B141">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="C141">
-        <v>15.0398</v>
-      </c>
-      <c r="D141" t="s">
-        <v>710</v>
+        <v>74.983699999999999</v>
       </c>
       <c r="E141" s="2">
         <v>46140</v>
       </c>
+      <c r="F141" s="1"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
-        <v>760</v>
+      <c r="A142" s="1" t="s">
+        <v>765</v>
       </c>
       <c r="B142">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="C142">
-        <v>74.956400000000002</v>
+        <v>11.9217</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>223</v>
       </c>
       <c r="E142" s="2">
         <v>46140</v>
@@ -18335,14 +18385,17 @@
       <c r="F142" s="1"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
-        <v>760</v>
+      <c r="A143" s="1" t="s">
+        <v>708</v>
       </c>
       <c r="B143">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C143">
-        <v>74.961699999999993</v>
+        <v>11.4803</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>705</v>
       </c>
       <c r="E143" s="2">
         <v>46140</v>
@@ -18350,14 +18403,17 @@
       <c r="F143" s="1"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>108</v>
+      <c r="A144" s="1" t="s">
+        <v>473</v>
       </c>
       <c r="B144">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C144">
-        <v>20.435700000000001</v>
+        <v>12.7316</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>419</v>
       </c>
       <c r="E144" s="2">
         <v>46140</v>
@@ -18366,16 +18422,13 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>229</v>
+        <v>760</v>
       </c>
       <c r="B145">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C145">
-        <v>10.076000000000001</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>228</v>
+        <v>74.984099999999998</v>
       </c>
       <c r="E145" s="2">
         <v>46140</v>
@@ -18384,16 +18437,16 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>33</v>
+        <v>242</v>
       </c>
       <c r="B146">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C146">
-        <v>13.6595</v>
+        <v>8.6835000000000004</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>30</v>
+        <v>715</v>
       </c>
       <c r="E146" s="2">
         <v>46140</v>
@@ -18402,16 +18455,13 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>35</v>
+        <v>760</v>
       </c>
       <c r="B147">
         <v>24</v>
       </c>
       <c r="C147">
-        <v>8.1547999999999998</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>30</v>
+        <v>74.984300000000005</v>
       </c>
       <c r="E147" s="2">
         <v>46140</v>
@@ -18420,16 +18470,16 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>537</v>
+        <v>222</v>
       </c>
       <c r="B148">
         <v>24</v>
       </c>
       <c r="C148">
-        <v>11.1936</v>
+        <v>15.422599999999999</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="E148" s="2">
         <v>46140</v>
@@ -18438,16 +18488,16 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>764</v>
+        <v>538</v>
       </c>
       <c r="B149">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C149">
-        <v>8.8575999999999997</v>
+        <v>11.7668</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>233</v>
+        <v>720</v>
       </c>
       <c r="E149" s="2">
         <v>46140</v>
@@ -18456,13 +18506,16 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B150">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C150">
-        <v>74.983699999999999</v>
+        <v>5.9949000000000003</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>233</v>
       </c>
       <c r="E150" s="2">
         <v>46140</v>
@@ -18471,16 +18524,16 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>765</v>
+        <v>427</v>
       </c>
       <c r="B151">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C151">
-        <v>11.9217</v>
+        <v>17.051500000000001</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>223</v>
+        <v>424</v>
       </c>
       <c r="E151" s="2">
         <v>46140</v>
@@ -18489,16 +18542,16 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>52</v>
+        <v>246</v>
       </c>
       <c r="B152">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C152">
-        <v>14.3188</v>
+        <v>6.0857999999999999</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>12</v>
+        <v>228</v>
       </c>
       <c r="E152" s="2">
         <v>46140</v>
@@ -18507,16 +18560,16 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>708</v>
+        <v>72</v>
       </c>
       <c r="B153">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C153">
-        <v>11.4803</v>
+        <v>7.6868999999999996</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>705</v>
+        <v>39</v>
       </c>
       <c r="E153" s="2">
         <v>46140</v>
@@ -18525,16 +18578,16 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>473</v>
+        <v>435</v>
       </c>
       <c r="B154">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C154">
-        <v>12.7316</v>
+        <v>10.0076</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>419</v>
+        <v>535</v>
       </c>
       <c r="E154" s="2">
         <v>46140</v>
@@ -18543,13 +18596,16 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>760</v>
+        <v>483</v>
       </c>
       <c r="B155">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C155">
-        <v>74.984099999999998</v>
+        <v>6.6196000000000002</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>535</v>
       </c>
       <c r="E155" s="2">
         <v>46140</v>
@@ -18558,16 +18614,16 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>242</v>
+        <v>74</v>
       </c>
       <c r="B156">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C156">
-        <v>8.6835000000000004</v>
+        <v>9.4603000000000002</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>715</v>
+        <v>39</v>
       </c>
       <c r="E156" s="2">
         <v>46140</v>
@@ -18576,16 +18632,16 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>327</v>
+        <v>518</v>
       </c>
       <c r="B157">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C157">
-        <v>10.024699999999999</v>
+        <v>7.4116999999999997</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>324</v>
+        <v>520</v>
       </c>
       <c r="E157" s="2">
         <v>46140</v>
@@ -18594,16 +18650,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>323</v>
+        <v>68</v>
       </c>
       <c r="B158">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="C158">
-        <v>12.001799999999999</v>
+        <v>7.9580000000000002</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>324</v>
+        <v>30</v>
       </c>
       <c r="E158" s="2">
         <v>46140</v>
@@ -18615,10 +18671,10 @@
         <v>760</v>
       </c>
       <c r="B159">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C159">
-        <v>74.984300000000005</v>
+        <v>74.982600000000005</v>
       </c>
       <c r="E159" s="2">
         <v>46140</v>
@@ -18627,314 +18683,299 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="B160">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C160">
-        <v>15.422599999999999</v>
+        <v>9.5602999999999998</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>715</v>
+        <v>218</v>
       </c>
       <c r="E160" s="2">
         <v>46140</v>
       </c>
-      <c r="F160" s="1"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>538</v>
+        <v>719</v>
       </c>
       <c r="B161">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C161">
-        <v>11.7668</v>
+        <v>10.0602</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>720</v>
+        <v>434</v>
       </c>
       <c r="E161" s="2">
         <v>46140</v>
       </c>
-      <c r="F161" s="1"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>766</v>
+        <v>70</v>
       </c>
       <c r="B162">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C162">
-        <v>5.9949000000000003</v>
+        <v>8.2233999999999998</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>233</v>
+        <v>30</v>
       </c>
       <c r="E162" s="2">
         <v>46140</v>
       </c>
-      <c r="F162" s="1"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
-        <v>427</v>
+        <v>466</v>
       </c>
       <c r="B163">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C163">
-        <v>17.051500000000001</v>
+        <v>6.0327000000000002</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>424</v>
+        <v>535</v>
       </c>
       <c r="E163" s="2">
         <v>46140</v>
       </c>
-      <c r="F163" s="1"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>246</v>
+        <v>716</v>
       </c>
       <c r="B164">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C164">
-        <v>6.0857999999999999</v>
+        <v>7.9481000000000002</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>228</v>
+        <v>530</v>
       </c>
       <c r="E164" s="2">
         <v>46140</v>
       </c>
-      <c r="F164" s="1"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="B165">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C165">
-        <v>7.6868999999999996</v>
+        <v>7.6905000000000001</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>39</v>
+        <v>228</v>
       </c>
       <c r="E165" s="2">
         <v>46140</v>
       </c>
-      <c r="F165" s="1"/>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>435</v>
+        <v>760</v>
       </c>
       <c r="B166">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C166">
-        <v>10.0076</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>535</v>
+        <v>74.982500000000002</v>
       </c>
       <c r="E166" s="2">
         <v>46140</v>
       </c>
-      <c r="F166" s="1"/>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A167" s="1" t="s">
-        <v>483</v>
+      <c r="A167" t="s">
+        <v>760</v>
       </c>
       <c r="B167">
         <v>24</v>
       </c>
       <c r="C167">
-        <v>6.6196000000000002</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>535</v>
+        <v>74.994600000000005</v>
       </c>
       <c r="E167" s="2">
         <v>46140</v>
       </c>
-      <c r="F167" s="1"/>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A168" s="1" t="s">
-        <v>74</v>
+      <c r="A168" t="s">
+        <v>325</v>
       </c>
       <c r="B168">
         <v>24</v>
       </c>
       <c r="C168">
-        <v>9.4603000000000002</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>39</v>
+        <v>10.173</v>
+      </c>
+      <c r="D168" t="s">
+        <v>324</v>
       </c>
       <c r="E168" s="2">
         <v>46140</v>
       </c>
-      <c r="F168" s="1"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A169" s="1" t="s">
-        <v>518</v>
+      <c r="A169" t="s">
+        <v>44</v>
       </c>
       <c r="B169">
         <v>24</v>
       </c>
       <c r="C169">
-        <v>7.4116999999999997</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>520</v>
+        <v>13.6996</v>
+      </c>
+      <c r="D169" t="s">
+        <v>39</v>
       </c>
       <c r="E169" s="2">
         <v>46140</v>
       </c>
-      <c r="F169" s="1"/>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A170" s="1" t="s">
-        <v>68</v>
+      <c r="A170" t="s">
+        <v>761</v>
       </c>
       <c r="B170">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C170">
-        <v>7.9580000000000002</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>30</v>
+        <v>18.021899999999999</v>
+      </c>
+      <c r="D170" t="s">
+        <v>223</v>
       </c>
       <c r="E170" s="2">
         <v>46140</v>
       </c>
-      <c r="F170" s="1"/>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A171" s="1" t="s">
-        <v>760</v>
+      <c r="A171" t="s">
+        <v>31</v>
       </c>
       <c r="B171">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C171">
-        <v>74.982600000000005</v>
+        <v>9.4723000000000006</v>
+      </c>
+      <c r="D171" t="s">
+        <v>30</v>
       </c>
       <c r="E171" s="2">
         <v>46140</v>
       </c>
-      <c r="F171" s="1"/>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A172" s="1" t="s">
-        <v>239</v>
+      <c r="A172" t="s">
+        <v>243</v>
       </c>
       <c r="B172">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C172">
-        <v>9.5602999999999998</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>218</v>
+        <v>11.8279</v>
+      </c>
+      <c r="D172" t="s">
+        <v>715</v>
       </c>
       <c r="E172" s="2">
         <v>46140</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A173" s="1" t="s">
-        <v>719</v>
+      <c r="A173" t="s">
+        <v>717</v>
       </c>
       <c r="B173">
         <v>23.9</v>
       </c>
       <c r="C173">
-        <v>10.0602</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>434</v>
+        <v>8.2769999999999992</v>
+      </c>
+      <c r="D173" t="s">
+        <v>530</v>
       </c>
       <c r="E173" s="2">
         <v>46140</v>
       </c>
+      <c r="F173" t="s">
+        <v>775</v>
+      </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A174" s="1" t="s">
-        <v>70</v>
+      <c r="A174" t="s">
+        <v>760</v>
       </c>
       <c r="B174">
         <v>23.9</v>
       </c>
       <c r="C174">
-        <v>8.2233999999999998</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>30</v>
+        <v>74.992099999999994</v>
       </c>
       <c r="E174" s="2">
         <v>46140</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A175" s="1" t="s">
-        <v>466</v>
+      <c r="A175" t="s">
+        <v>422</v>
       </c>
       <c r="B175">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="C175">
-        <v>6.0327000000000002</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>535</v>
+        <v>11.6334</v>
+      </c>
+      <c r="D175" t="s">
+        <v>419</v>
       </c>
       <c r="E175" s="2">
         <v>46140</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A176" s="1" t="s">
-        <v>716</v>
+      <c r="A176" t="s">
+        <v>244</v>
       </c>
       <c r="B176">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="C176">
-        <v>7.9481000000000002</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>530</v>
+        <v>12.891400000000001</v>
+      </c>
+      <c r="D176" t="s">
+        <v>715</v>
       </c>
       <c r="E176" s="2">
         <v>46140</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A177" s="1" t="s">
-        <v>54</v>
+      <c r="A177" t="s">
+        <v>423</v>
       </c>
       <c r="B177">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="C177">
-        <v>9.4989000000000008</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>12</v>
+        <v>10.247</v>
+      </c>
+      <c r="D177" t="s">
+        <v>424</v>
       </c>
       <c r="E177" s="2">
         <v>46140</v>
@@ -18942,440 +18983,449 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>231</v>
+        <v>760</v>
       </c>
       <c r="B178">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C178">
-        <v>7.6905000000000001</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>228</v>
+        <v>74.9863</v>
       </c>
       <c r="E178" s="2">
-        <v>46140</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
-        <v>760</v>
+        <v>230</v>
       </c>
       <c r="B179">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C179">
-        <v>74.982500000000002</v>
+        <v>10.781599999999999</v>
+      </c>
+      <c r="D179" t="s">
+        <v>228</v>
       </c>
       <c r="E179" s="2">
-        <v>46140</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A180" t="s">
-        <v>760</v>
+      <c r="A180" s="1" t="s">
+        <v>322</v>
       </c>
       <c r="B180">
         <v>24</v>
       </c>
       <c r="C180">
-        <v>74.994600000000005</v>
+        <v>10.1585</v>
+      </c>
+      <c r="D180" t="s">
+        <v>319</v>
       </c>
       <c r="E180" s="2">
-        <v>46140</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A181" t="s">
-        <v>325</v>
+      <c r="A181" s="1" t="s">
+        <v>768</v>
       </c>
       <c r="B181">
         <v>24</v>
       </c>
       <c r="C181">
-        <v>10.173</v>
+        <v>5.9733999999999998</v>
       </c>
       <c r="D181" t="s">
-        <v>324</v>
+        <v>233</v>
       </c>
       <c r="E181" s="2">
-        <v>46140</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A182" t="s">
-        <v>44</v>
+      <c r="A182" s="1" t="s">
+        <v>712</v>
       </c>
       <c r="B182">
         <v>24</v>
       </c>
       <c r="C182">
-        <v>13.6996</v>
+        <v>7.5457000000000001</v>
       </c>
       <c r="D182" t="s">
-        <v>39</v>
+        <v>710</v>
       </c>
       <c r="E182" s="2">
-        <v>46140</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A183" t="s">
-        <v>761</v>
+      <c r="A183" s="1" t="s">
+        <v>760</v>
       </c>
       <c r="B183">
+        <v>24.1</v>
+      </c>
+      <c r="C183">
+        <v>74.981200000000001</v>
+      </c>
+      <c r="E183" s="2">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A184" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B184">
+        <v>24.1</v>
+      </c>
+      <c r="C184">
+        <v>9.0748999999999995</v>
+      </c>
+      <c r="D184" t="s">
+        <v>434</v>
+      </c>
+      <c r="E184" s="2">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A185" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B185">
+        <v>24.1</v>
+      </c>
+      <c r="C185">
+        <v>10.447100000000001</v>
+      </c>
+      <c r="D185" t="s">
+        <v>223</v>
+      </c>
+      <c r="E185" s="2">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A186" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B186">
+        <v>24.1</v>
+      </c>
+      <c r="C186">
+        <v>7.6365999999999996</v>
+      </c>
+      <c r="D186" t="s">
+        <v>535</v>
+      </c>
+      <c r="E186" s="2">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A187" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B187">
+        <v>24.1</v>
+      </c>
+      <c r="C187">
+        <v>10.598800000000001</v>
+      </c>
+      <c r="D187" t="s">
+        <v>419</v>
+      </c>
+      <c r="E187" s="2">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A188" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B188">
+        <v>24.1</v>
+      </c>
+      <c r="C188">
+        <v>7.3235000000000001</v>
+      </c>
+      <c r="D188" t="s">
+        <v>12</v>
+      </c>
+      <c r="E188" s="2">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A189" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B189">
+        <v>24.1</v>
+      </c>
+      <c r="C189">
+        <v>12.1478</v>
+      </c>
+      <c r="D189" t="s">
+        <v>715</v>
+      </c>
+      <c r="E189" s="2">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A190" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B190">
         <v>24</v>
       </c>
-      <c r="C183">
-        <v>18.021899999999999</v>
-      </c>
-      <c r="D183" t="s">
-        <v>223</v>
-      </c>
-      <c r="E183" s="2">
-        <v>46140</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A184" t="s">
-        <v>220</v>
-      </c>
-      <c r="B184">
-        <v>24</v>
-      </c>
-      <c r="C184">
-        <v>8.1714000000000002</v>
-      </c>
-      <c r="D184" t="s">
-        <v>218</v>
-      </c>
-      <c r="E184" s="2">
-        <v>46140</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A185" t="s">
-        <v>31</v>
-      </c>
-      <c r="B185">
-        <v>24</v>
-      </c>
-      <c r="C185">
-        <v>9.4723000000000006</v>
-      </c>
-      <c r="D185" t="s">
-        <v>30</v>
-      </c>
-      <c r="E185" s="2">
-        <v>46140</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A186" t="s">
-        <v>243</v>
-      </c>
-      <c r="B186">
-        <v>24</v>
-      </c>
-      <c r="C186">
-        <v>11.8279</v>
-      </c>
-      <c r="D186" t="s">
-        <v>715</v>
-      </c>
-      <c r="E186" s="2">
-        <v>46140</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A187" t="s">
-        <v>717</v>
-      </c>
-      <c r="B187">
-        <v>23.9</v>
-      </c>
-      <c r="C187">
-        <v>8.2769999999999992</v>
-      </c>
-      <c r="D187" t="s">
-        <v>434</v>
-      </c>
-      <c r="E187" s="2">
-        <v>46140</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A188" t="s">
-        <v>760</v>
-      </c>
-      <c r="B188">
-        <v>23.9</v>
-      </c>
-      <c r="C188">
-        <v>74.992099999999994</v>
-      </c>
-      <c r="E188" s="2">
-        <v>46140</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A189" t="s">
-        <v>422</v>
-      </c>
-      <c r="B189">
-        <v>23.9</v>
-      </c>
-      <c r="C189">
-        <v>11.6334</v>
-      </c>
-      <c r="D189" t="s">
-        <v>419</v>
-      </c>
-      <c r="E189" s="2">
-        <v>46140</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A190" t="s">
-        <v>244</v>
-      </c>
-      <c r="B190">
-        <v>23.9</v>
-      </c>
       <c r="C190">
-        <v>12.891400000000001</v>
-      </c>
-      <c r="D190" t="s">
-        <v>715</v>
+        <v>74.979799999999997</v>
       </c>
       <c r="E190" s="2">
-        <v>46140</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>423</v>
+        <v>216</v>
       </c>
       <c r="B191">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C191">
-        <v>10.247</v>
+        <v>15.5242</v>
       </c>
       <c r="D191" t="s">
-        <v>424</v>
+        <v>218</v>
       </c>
       <c r="E191" s="2">
-        <v>46140</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A192" s="1" t="s">
-        <v>760</v>
+      <c r="A192" t="s">
+        <v>269</v>
       </c>
       <c r="B192">
         <v>24</v>
       </c>
       <c r="C192">
-        <v>74.9863</v>
+        <v>8.3556000000000008</v>
+      </c>
+      <c r="D192" t="s">
+        <v>218</v>
       </c>
       <c r="E192" s="2">
         <v>46141</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A193" s="1" t="s">
-        <v>230</v>
+      <c r="A193" t="s">
+        <v>219</v>
       </c>
       <c r="B193">
         <v>24</v>
       </c>
       <c r="C193">
-        <v>10.781599999999999</v>
+        <v>9.0799000000000003</v>
       </c>
       <c r="D193" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="E193" s="2">
         <v>46141</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A194" s="1" t="s">
-        <v>322</v>
+      <c r="A194" t="s">
+        <v>270</v>
       </c>
       <c r="B194">
         <v>24</v>
       </c>
       <c r="C194">
-        <v>10.1585</v>
+        <v>7.9066999999999998</v>
       </c>
       <c r="D194" t="s">
-        <v>319</v>
+        <v>218</v>
       </c>
       <c r="E194" s="2">
         <v>46141</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A195" s="1" t="s">
-        <v>768</v>
+      <c r="A195" t="s">
+        <v>220</v>
       </c>
       <c r="B195">
         <v>24</v>
       </c>
       <c r="C195">
-        <v>5.9733999999999998</v>
+        <v>8.2003000000000004</v>
       </c>
       <c r="D195" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="E195" s="2">
         <v>46141</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A196" s="1" t="s">
-        <v>712</v>
+      <c r="A196" t="s">
+        <v>271</v>
       </c>
       <c r="B196">
         <v>24</v>
       </c>
       <c r="C196">
-        <v>7.5457000000000001</v>
+        <v>11.0288</v>
       </c>
       <c r="D196" t="s">
-        <v>710</v>
+        <v>218</v>
       </c>
       <c r="E196" s="2">
         <v>46141</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A197" s="1" t="s">
-        <v>760</v>
+      <c r="A197" t="s">
+        <v>221</v>
       </c>
       <c r="B197">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C197">
-        <v>74.981200000000001</v>
+        <v>11.9969</v>
+      </c>
+      <c r="D197" t="s">
+        <v>218</v>
       </c>
       <c r="E197" s="2">
         <v>46141</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A198" s="1" t="s">
-        <v>722</v>
+      <c r="A198" t="s">
+        <v>272</v>
       </c>
       <c r="B198">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C198">
-        <v>9.0748999999999995</v>
+        <v>9.0746000000000002</v>
       </c>
       <c r="D198" t="s">
-        <v>434</v>
+        <v>218</v>
       </c>
       <c r="E198" s="2">
         <v>46141</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A199" s="1" t="s">
-        <v>769</v>
+      <c r="A199" t="s">
+        <v>285</v>
       </c>
       <c r="B199">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C199">
-        <v>10.447100000000001</v>
+        <v>6.4494999999999996</v>
       </c>
       <c r="D199" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E199" s="2">
         <v>46141</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A200" s="1" t="s">
-        <v>433</v>
+      <c r="A200" t="s">
+        <v>286</v>
       </c>
       <c r="B200">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C200">
-        <v>7.6365999999999996</v>
+        <v>10.295199999999999</v>
       </c>
       <c r="D200" t="s">
-        <v>535</v>
+        <v>218</v>
       </c>
       <c r="E200" s="2">
         <v>46141</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A201" s="1" t="s">
-        <v>420</v>
+      <c r="A201" t="s">
+        <v>287</v>
       </c>
       <c r="B201">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C201">
-        <v>10.598800000000001</v>
+        <v>6.6711999999999998</v>
       </c>
       <c r="D201" t="s">
-        <v>419</v>
+        <v>218</v>
       </c>
       <c r="E201" s="2">
         <v>46141</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A202" s="1" t="s">
-        <v>50</v>
+      <c r="A202" t="s">
+        <v>240</v>
       </c>
       <c r="B202">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C202">
-        <v>7.3235000000000001</v>
+        <v>9.0074000000000005</v>
       </c>
       <c r="D202" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="E202" s="2">
         <v>46141</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A203" s="1" t="s">
-        <v>241</v>
+      <c r="A203" t="s">
+        <v>288</v>
       </c>
       <c r="B203">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C203">
-        <v>12.1478</v>
+        <v>9.1846999999999994</v>
       </c>
       <c r="D203" t="s">
-        <v>715</v>
+        <v>218</v>
       </c>
       <c r="E203" s="2">
         <v>46141</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A204" s="1" t="s">
-        <v>760</v>
+      <c r="A204" t="s">
+        <v>253</v>
       </c>
       <c r="B204">
         <v>24</v>
       </c>
       <c r="C204">
-        <v>74.979799999999997</v>
+        <v>17.3188</v>
+      </c>
+      <c r="D204" t="s">
+        <v>218</v>
       </c>
       <c r="E204" s="2">
         <v>46141</v>
@@ -19383,13 +19433,13 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>216</v>
+        <v>301</v>
       </c>
       <c r="B205">
         <v>24</v>
       </c>
       <c r="C205">
-        <v>15.5242</v>
+        <v>32.707900000000002</v>
       </c>
       <c r="D205" t="s">
         <v>218</v>
@@ -19400,13 +19450,13 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="B206">
         <v>24</v>
       </c>
       <c r="C206">
-        <v>8.3556000000000008</v>
+        <v>26.037199999999999</v>
       </c>
       <c r="D206" t="s">
         <v>218</v>
@@ -19417,13 +19467,13 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>219</v>
+        <v>302</v>
       </c>
       <c r="B207">
         <v>24</v>
       </c>
       <c r="C207">
-        <v>9.0799000000000003</v>
+        <v>26.700600000000001</v>
       </c>
       <c r="D207" t="s">
         <v>218</v>
@@ -19434,13 +19484,13 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="B208">
         <v>24</v>
       </c>
       <c r="C208">
-        <v>7.9066999999999998</v>
+        <v>19.355499999999999</v>
       </c>
       <c r="D208" t="s">
         <v>218</v>
@@ -19451,13 +19501,13 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>220</v>
+        <v>303</v>
       </c>
       <c r="B209">
         <v>24</v>
       </c>
       <c r="C209">
-        <v>8.2003000000000004</v>
+        <v>14.1128</v>
       </c>
       <c r="D209" t="s">
         <v>218</v>
@@ -19468,13 +19518,13 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="B210">
         <v>24</v>
       </c>
       <c r="C210">
-        <v>11.0288</v>
+        <v>10.949400000000001</v>
       </c>
       <c r="D210" t="s">
         <v>218</v>
@@ -19485,13 +19535,13 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>221</v>
+        <v>304</v>
       </c>
       <c r="B211">
         <v>24</v>
       </c>
       <c r="C211">
-        <v>11.9969</v>
+        <v>13.963200000000001</v>
       </c>
       <c r="D211" t="s">
         <v>218</v>
@@ -19502,16 +19552,13 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>272</v>
+        <v>760</v>
       </c>
       <c r="B212">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C212">
-        <v>9.0746000000000002</v>
-      </c>
-      <c r="D212" t="s">
-        <v>218</v>
+        <v>74.984200000000001</v>
       </c>
       <c r="E212" s="2">
         <v>46141</v>
@@ -19519,16 +19566,16 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>285</v>
+        <v>418</v>
       </c>
       <c r="B213">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C213">
-        <v>6.4494999999999996</v>
+        <v>7.9984999999999999</v>
       </c>
       <c r="D213" t="s">
-        <v>218</v>
+        <v>419</v>
       </c>
       <c r="E213" s="2">
         <v>46141</v>
@@ -19536,16 +19583,16 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>286</v>
+        <v>438</v>
       </c>
       <c r="B214">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C214">
-        <v>10.295199999999999</v>
+        <v>10.8348</v>
       </c>
       <c r="D214" t="s">
-        <v>218</v>
+        <v>419</v>
       </c>
       <c r="E214" s="2">
         <v>46141</v>
@@ -19553,16 +19600,16 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>287</v>
+        <v>454</v>
       </c>
       <c r="B215">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C215">
-        <v>6.6711999999999998</v>
+        <v>9.8247999999999998</v>
       </c>
       <c r="D215" t="s">
-        <v>218</v>
+        <v>419</v>
       </c>
       <c r="E215" s="2">
         <v>46141</v>
@@ -19570,16 +19617,16 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>240</v>
+        <v>470</v>
       </c>
       <c r="B216">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C216">
-        <v>9.0074000000000005</v>
+        <v>8.6006999999999998</v>
       </c>
       <c r="D216" t="s">
-        <v>218</v>
+        <v>419</v>
       </c>
       <c r="E216" s="2">
         <v>46141</v>
@@ -19587,16 +19634,16 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>288</v>
+        <v>486</v>
       </c>
       <c r="B217">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C217">
-        <v>9.1846999999999994</v>
+        <v>5.7709000000000001</v>
       </c>
       <c r="D217" t="s">
-        <v>218</v>
+        <v>419</v>
       </c>
       <c r="E217" s="2">
         <v>46141</v>
@@ -19604,16 +19651,13 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>253</v>
+        <v>760</v>
       </c>
       <c r="B218">
         <v>24</v>
       </c>
       <c r="C218">
-        <v>17.3188</v>
-      </c>
-      <c r="D218" t="s">
-        <v>218</v>
+        <v>74.979500000000002</v>
       </c>
       <c r="E218" s="2">
         <v>46141</v>
@@ -19621,16 +19665,16 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>301</v>
+        <v>502</v>
       </c>
       <c r="B219">
         <v>24</v>
       </c>
       <c r="C219">
-        <v>32.707900000000002</v>
+        <v>9.1074000000000002</v>
       </c>
       <c r="D219" t="s">
-        <v>218</v>
+        <v>419</v>
       </c>
       <c r="E219" s="2">
         <v>46141</v>
@@ -19638,16 +19682,16 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>254</v>
+        <v>439</v>
       </c>
       <c r="B220">
         <v>24</v>
       </c>
       <c r="C220">
-        <v>26.037199999999999</v>
+        <v>9.6449999999999996</v>
       </c>
       <c r="D220" t="s">
-        <v>218</v>
+        <v>419</v>
       </c>
       <c r="E220" s="2">
         <v>46141</v>
@@ -19655,16 +19699,16 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>302</v>
+        <v>455</v>
       </c>
       <c r="B221">
         <v>24</v>
       </c>
       <c r="C221">
-        <v>26.700600000000001</v>
+        <v>13.5069</v>
       </c>
       <c r="D221" t="s">
-        <v>218</v>
+        <v>419</v>
       </c>
       <c r="E221" s="2">
         <v>46141</v>
@@ -19672,16 +19716,16 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>255</v>
+        <v>471</v>
       </c>
       <c r="B222">
         <v>24</v>
       </c>
       <c r="C222">
-        <v>19.355499999999999</v>
+        <v>9.3131000000000004</v>
       </c>
       <c r="D222" t="s">
-        <v>218</v>
+        <v>419</v>
       </c>
       <c r="E222" s="2">
         <v>46141</v>
@@ -19689,16 +19733,16 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>303</v>
+        <v>487</v>
       </c>
       <c r="B223">
         <v>24</v>
       </c>
       <c r="C223">
-        <v>14.1128</v>
+        <v>10.4513</v>
       </c>
       <c r="D223" t="s">
-        <v>218</v>
+        <v>419</v>
       </c>
       <c r="E223" s="2">
         <v>46141</v>
@@ -19706,16 +19750,16 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>256</v>
+        <v>421</v>
       </c>
       <c r="B224">
         <v>24</v>
       </c>
       <c r="C224">
-        <v>10.949400000000001</v>
+        <v>8.8019999999999996</v>
       </c>
       <c r="D224" t="s">
-        <v>218</v>
+        <v>419</v>
       </c>
       <c r="E224" s="2">
         <v>46141</v>
@@ -19723,16 +19767,16 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>304</v>
+        <v>440</v>
       </c>
       <c r="B225">
         <v>24</v>
       </c>
       <c r="C225">
-        <v>13.963200000000001</v>
+        <v>9.9923999999999999</v>
       </c>
       <c r="D225" t="s">
-        <v>218</v>
+        <v>419</v>
       </c>
       <c r="E225" s="2">
         <v>46141</v>
@@ -19740,13 +19784,16 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>760</v>
+        <v>472</v>
       </c>
       <c r="B226">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C226">
-        <v>74.984200000000001</v>
+        <v>7.2567000000000004</v>
+      </c>
+      <c r="D226" t="s">
+        <v>419</v>
       </c>
       <c r="E226" s="2">
         <v>46141</v>
@@ -19754,13 +19801,13 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>418</v>
+        <v>488</v>
       </c>
       <c r="B227">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C227">
-        <v>7.9984999999999999</v>
+        <v>6.7808000000000002</v>
       </c>
       <c r="D227" t="s">
         <v>419</v>
@@ -19771,13 +19818,13 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>438</v>
+        <v>504</v>
       </c>
       <c r="B228">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C228">
-        <v>10.8348</v>
+        <v>8.1574000000000009</v>
       </c>
       <c r="D228" t="s">
         <v>419</v>
@@ -19788,13 +19835,13 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="B229">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C229">
-        <v>9.8247999999999998</v>
+        <v>11.8635</v>
       </c>
       <c r="D229" t="s">
         <v>419</v>
@@ -19805,13 +19852,13 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="B230">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C230">
-        <v>8.6006999999999998</v>
+        <v>9.5657999999999994</v>
       </c>
       <c r="D230" t="s">
         <v>419</v>
@@ -19822,13 +19869,13 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B231">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C231">
-        <v>5.7709000000000001</v>
+        <v>18.431799999999999</v>
       </c>
       <c r="D231" t="s">
         <v>419</v>
@@ -19839,13 +19886,16 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>760</v>
+        <v>505</v>
       </c>
       <c r="B232">
         <v>24</v>
       </c>
       <c r="C232">
-        <v>74.979500000000002</v>
+        <v>10.849600000000001</v>
+      </c>
+      <c r="D232" t="s">
+        <v>419</v>
       </c>
       <c r="E232" s="2">
         <v>46141</v>
@@ -19853,16 +19903,16 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>502</v>
+        <v>718</v>
       </c>
       <c r="B233">
         <v>24</v>
       </c>
       <c r="C233">
-        <v>9.1074000000000002</v>
+        <v>7.2061999999999999</v>
       </c>
       <c r="D233" t="s">
-        <v>419</v>
+        <v>530</v>
       </c>
       <c r="E233" s="2">
         <v>46141</v>
@@ -19870,16 +19920,16 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>439</v>
+        <v>522</v>
       </c>
       <c r="B234">
         <v>24</v>
       </c>
       <c r="C234">
-        <v>9.6449999999999996</v>
+        <v>10.3369</v>
       </c>
       <c r="D234" t="s">
-        <v>419</v>
+        <v>520</v>
       </c>
       <c r="E234" s="2">
         <v>46141</v>
@@ -19887,16 +19937,16 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>455</v>
+        <v>523</v>
       </c>
       <c r="B235">
         <v>24</v>
       </c>
       <c r="C235">
-        <v>13.5069</v>
+        <v>11.719200000000001</v>
       </c>
       <c r="D235" t="s">
-        <v>419</v>
+        <v>520</v>
       </c>
       <c r="E235" s="2">
         <v>46141</v>
@@ -19904,16 +19954,13 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>471</v>
+        <v>760</v>
       </c>
       <c r="B236">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C236">
-        <v>9.3131000000000004</v>
-      </c>
-      <c r="D236" t="s">
-        <v>419</v>
+        <v>74.985600000000005</v>
       </c>
       <c r="E236" s="2">
         <v>46141</v>
@@ -19921,16 +19968,16 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>487</v>
+        <v>320</v>
       </c>
       <c r="B237">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C237">
-        <v>10.4513</v>
+        <v>14.5794</v>
       </c>
       <c r="D237" t="s">
-        <v>419</v>
+        <v>319</v>
       </c>
       <c r="E237" s="2">
         <v>46141</v>
@@ -19938,16 +19985,16 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>421</v>
+        <v>721</v>
       </c>
       <c r="B238">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C238">
-        <v>8.8019999999999996</v>
+        <v>7.9523000000000001</v>
       </c>
       <c r="D238" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="E238" s="2">
         <v>46141</v>
@@ -19955,16 +20002,16 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>440</v>
+        <v>237</v>
       </c>
       <c r="B239">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C239">
-        <v>9.9923999999999999</v>
+        <v>15.263</v>
       </c>
       <c r="D239" t="s">
-        <v>419</v>
+        <v>218</v>
       </c>
       <c r="E239" s="2">
         <v>46141</v>
@@ -19972,13 +20019,13 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="B240">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C240">
-        <v>7.2567000000000004</v>
+        <v>11.4131</v>
       </c>
       <c r="D240" t="s">
         <v>419</v>
@@ -19989,16 +20036,13 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>488</v>
+        <v>760</v>
       </c>
       <c r="B241">
         <v>24</v>
       </c>
       <c r="C241">
-        <v>6.7808000000000002</v>
-      </c>
-      <c r="D241" t="s">
-        <v>419</v>
+        <v>74.979900000000001</v>
       </c>
       <c r="E241" s="2">
         <v>46141</v>
@@ -20006,16 +20050,16 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>504</v>
+        <v>711</v>
       </c>
       <c r="B242">
         <v>24</v>
       </c>
       <c r="C242">
-        <v>8.1574000000000009</v>
+        <v>13.5703</v>
       </c>
       <c r="D242" t="s">
-        <v>419</v>
+        <v>710</v>
       </c>
       <c r="E242" s="2">
         <v>46141</v>
@@ -20023,16 +20067,16 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>441</v>
+        <v>534</v>
       </c>
       <c r="B243">
         <v>24</v>
       </c>
       <c r="C243">
-        <v>11.8635</v>
+        <v>9.4437999999999995</v>
       </c>
       <c r="D243" t="s">
-        <v>419</v>
+        <v>720</v>
       </c>
       <c r="E243" s="2">
         <v>46141</v>
@@ -20040,16 +20084,16 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>457</v>
+        <v>227</v>
       </c>
       <c r="B244">
         <v>24</v>
       </c>
       <c r="C244">
-        <v>9.5657999999999994</v>
+        <v>10.5215</v>
       </c>
       <c r="D244" t="s">
-        <v>419</v>
+        <v>228</v>
       </c>
       <c r="E244" s="2">
         <v>46141</v>
@@ -20057,16 +20101,16 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>489</v>
+        <v>770</v>
       </c>
       <c r="B245">
         <v>24</v>
       </c>
       <c r="C245">
-        <v>18.431799999999999</v>
+        <v>11.101000000000001</v>
       </c>
       <c r="D245" t="s">
-        <v>419</v>
+        <v>223</v>
       </c>
       <c r="E245" s="2">
         <v>46141</v>
@@ -20074,16 +20118,16 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>505</v>
+        <v>37</v>
       </c>
       <c r="B246">
         <v>24</v>
       </c>
       <c r="C246">
-        <v>10.849600000000001</v>
+        <v>9.6929999999999996</v>
       </c>
       <c r="D246" t="s">
-        <v>419</v>
+        <v>39</v>
       </c>
       <c r="E246" s="2">
         <v>46141</v>
@@ -20091,16 +20135,16 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>718</v>
+        <v>337</v>
       </c>
       <c r="B247">
         <v>24</v>
       </c>
       <c r="C247">
-        <v>7.2061999999999999</v>
+        <v>6.0260999999999996</v>
       </c>
       <c r="D247" t="s">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="E247" s="2">
         <v>46141</v>
@@ -20108,16 +20152,16 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>522</v>
+        <v>40</v>
       </c>
       <c r="B248">
         <v>24</v>
       </c>
       <c r="C248">
-        <v>10.3369</v>
+        <v>10.497999999999999</v>
       </c>
       <c r="D248" t="s">
-        <v>520</v>
+        <v>39</v>
       </c>
       <c r="E248" s="2">
         <v>46141</v>
@@ -20125,16 +20169,16 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>523</v>
+        <v>42</v>
       </c>
       <c r="B249">
         <v>24</v>
       </c>
       <c r="C249">
-        <v>11.719200000000001</v>
+        <v>9.9788999999999994</v>
       </c>
       <c r="D249" t="s">
-        <v>520</v>
+        <v>39</v>
       </c>
       <c r="E249" s="2">
         <v>46141</v>
@@ -20142,13 +20186,16 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>760</v>
+        <v>76</v>
       </c>
       <c r="B250">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C250">
-        <v>74.985600000000005</v>
+        <v>9.9703999999999997</v>
+      </c>
+      <c r="D250" t="s">
+        <v>39</v>
       </c>
       <c r="E250" s="2">
         <v>46141</v>
@@ -20156,16 +20203,16 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>320</v>
+        <v>78</v>
       </c>
       <c r="B251">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C251">
-        <v>14.5794</v>
+        <v>7.1820000000000004</v>
       </c>
       <c r="D251" t="s">
-        <v>319</v>
+        <v>39</v>
       </c>
       <c r="E251" s="2">
         <v>46141</v>
@@ -20173,16 +20220,16 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>721</v>
+        <v>106</v>
       </c>
       <c r="B252">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C252">
-        <v>7.9523000000000001</v>
+        <v>21.435700000000001</v>
       </c>
       <c r="D252" t="s">
-        <v>434</v>
+        <v>39</v>
       </c>
       <c r="E252" s="2">
         <v>46141</v>
@@ -20190,16 +20237,16 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>237</v>
+        <v>110</v>
       </c>
       <c r="B253">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C253">
-        <v>15.263</v>
+        <v>24.386299999999999</v>
       </c>
       <c r="D253" t="s">
-        <v>218</v>
+        <v>39</v>
       </c>
       <c r="E253" s="2">
         <v>46141</v>
@@ -20207,16 +20254,16 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>456</v>
+        <v>112</v>
       </c>
       <c r="B254">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C254">
-        <v>11.4131</v>
+        <v>18.008600000000001</v>
       </c>
       <c r="D254" t="s">
-        <v>419</v>
+        <v>39</v>
       </c>
       <c r="E254" s="2">
         <v>46141</v>
@@ -20224,13 +20271,16 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>760</v>
+        <v>140</v>
       </c>
       <c r="B255">
         <v>24</v>
       </c>
       <c r="C255">
-        <v>74.979900000000001</v>
+        <v>21.275500000000001</v>
+      </c>
+      <c r="D255" t="s">
+        <v>39</v>
       </c>
       <c r="E255" s="2">
         <v>46141</v>
@@ -20238,16 +20288,16 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>711</v>
+        <v>142</v>
       </c>
       <c r="B256">
         <v>24</v>
       </c>
       <c r="C256">
-        <v>13.5703</v>
+        <v>25.0242</v>
       </c>
       <c r="D256" t="s">
-        <v>710</v>
+        <v>39</v>
       </c>
       <c r="E256" s="2">
         <v>46141</v>
@@ -20255,16 +20305,16 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>534</v>
+        <v>144</v>
       </c>
       <c r="B257">
         <v>24</v>
       </c>
       <c r="C257">
-        <v>9.4437999999999995</v>
+        <v>20.784199999999998</v>
       </c>
       <c r="D257" t="s">
-        <v>720</v>
+        <v>39</v>
       </c>
       <c r="E257" s="2">
         <v>46141</v>
@@ -20272,16 +20322,13 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>227</v>
+        <v>760</v>
       </c>
       <c r="B258">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C258">
-        <v>10.5215</v>
-      </c>
-      <c r="D258" t="s">
-        <v>228</v>
+        <v>74.980099999999993</v>
       </c>
       <c r="E258" s="2">
         <v>46141</v>
@@ -20289,16 +20336,16 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>770</v>
+        <v>146</v>
       </c>
       <c r="B259">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C259">
-        <v>11.101000000000001</v>
+        <v>13.4788</v>
       </c>
       <c r="D259" t="s">
-        <v>223</v>
+        <v>39</v>
       </c>
       <c r="E259" s="2">
         <v>46141</v>
@@ -20306,13 +20353,13 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>37</v>
+        <v>174</v>
       </c>
       <c r="B260">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C260">
-        <v>9.6929999999999996</v>
+        <v>8.2649000000000008</v>
       </c>
       <c r="D260" t="s">
         <v>39</v>
@@ -20323,16 +20370,16 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>337</v>
+        <v>176</v>
       </c>
       <c r="B261">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C261">
-        <v>6.0260999999999996</v>
+        <v>4.7102000000000004</v>
       </c>
       <c r="D261" t="s">
-        <v>334</v>
+        <v>39</v>
       </c>
       <c r="E261" s="2">
         <v>46141</v>
@@ -20340,13 +20387,13 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>40</v>
+        <v>178</v>
       </c>
       <c r="B262">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C262">
-        <v>10.497999999999999</v>
+        <v>12.211600000000001</v>
       </c>
       <c r="D262" t="s">
         <v>39</v>
@@ -20357,13 +20404,13 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>42</v>
+        <v>180</v>
       </c>
       <c r="B263">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C263">
-        <v>9.9788999999999994</v>
+        <v>6.7732000000000001</v>
       </c>
       <c r="D263" t="s">
         <v>39</v>
@@ -20374,13 +20421,13 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>76</v>
+        <v>208</v>
       </c>
       <c r="B264">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C264">
-        <v>9.9703999999999997</v>
+        <v>20.435300000000002</v>
       </c>
       <c r="D264" t="s">
         <v>39</v>
@@ -20391,13 +20438,13 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>78</v>
+        <v>210</v>
       </c>
       <c r="B265">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C265">
-        <v>7.1820000000000004</v>
+        <v>20.806699999999999</v>
       </c>
       <c r="D265" t="s">
         <v>39</v>
@@ -20408,13 +20455,13 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>106</v>
+        <v>212</v>
       </c>
       <c r="B266">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C266">
-        <v>21.435700000000001</v>
+        <v>15.5441</v>
       </c>
       <c r="D266" t="s">
         <v>39</v>
@@ -20425,13 +20472,13 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>110</v>
+        <v>214</v>
       </c>
       <c r="B267">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C267">
-        <v>24.386299999999999</v>
+        <v>22.4376</v>
       </c>
       <c r="D267" t="s">
         <v>39</v>
@@ -20442,16 +20489,13 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>112</v>
+        <v>760</v>
       </c>
       <c r="B268">
         <v>24</v>
       </c>
       <c r="C268">
-        <v>18.008600000000001</v>
-      </c>
-      <c r="D268" t="s">
-        <v>39</v>
+        <v>74.988399999999999</v>
       </c>
       <c r="E268" s="2">
         <v>46141</v>
@@ -20459,16 +20503,16 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>140</v>
+        <v>450</v>
       </c>
       <c r="B269">
         <v>24</v>
       </c>
       <c r="C269">
-        <v>21.275500000000001</v>
+        <v>7.5002000000000004</v>
       </c>
       <c r="D269" t="s">
-        <v>39</v>
+        <v>535</v>
       </c>
       <c r="E269" s="2">
         <v>46141</v>
@@ -20476,16 +20520,16 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>142</v>
+        <v>482</v>
       </c>
       <c r="B270">
         <v>24</v>
       </c>
       <c r="C270">
-        <v>25.0242</v>
+        <v>6.1449999999999996</v>
       </c>
       <c r="D270" t="s">
-        <v>39</v>
+        <v>535</v>
       </c>
       <c r="E270" s="2">
         <v>46141</v>
@@ -20493,16 +20537,16 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>144</v>
+        <v>498</v>
       </c>
       <c r="B271">
         <v>24</v>
       </c>
       <c r="C271">
-        <v>20.784199999999998</v>
+        <v>5.9164000000000003</v>
       </c>
       <c r="D271" t="s">
-        <v>39</v>
+        <v>535</v>
       </c>
       <c r="E271" s="2">
         <v>46141</v>
@@ -20510,13 +20554,16 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>760</v>
+        <v>514</v>
       </c>
       <c r="B272">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C272">
-        <v>74.980099999999993</v>
+        <v>6.3282999999999996</v>
+      </c>
+      <c r="D272" t="s">
+        <v>535</v>
       </c>
       <c r="E272" s="2">
         <v>46141</v>
@@ -20524,16 +20571,16 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>146</v>
+        <v>451</v>
       </c>
       <c r="B273">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C273">
-        <v>13.4788</v>
+        <v>5.2625999999999999</v>
       </c>
       <c r="D273" t="s">
-        <v>39</v>
+        <v>535</v>
       </c>
       <c r="E273" s="2">
         <v>46141</v>
@@ -20541,16 +20588,16 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>174</v>
+        <v>467</v>
       </c>
       <c r="B274">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C274">
-        <v>8.2649000000000008</v>
+        <v>9.2093000000000007</v>
       </c>
       <c r="D274" t="s">
-        <v>39</v>
+        <v>535</v>
       </c>
       <c r="E274" s="2">
         <v>46141</v>
@@ -20558,16 +20605,16 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>176</v>
+        <v>499</v>
       </c>
       <c r="B275">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C275">
-        <v>4.7102000000000004</v>
+        <v>6.3968999999999996</v>
       </c>
       <c r="D275" t="s">
-        <v>39</v>
+        <v>535</v>
       </c>
       <c r="E275" s="2">
         <v>46141</v>
@@ -20575,16 +20622,16 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>178</v>
+        <v>515</v>
       </c>
       <c r="B276">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C276">
-        <v>12.211600000000001</v>
+        <v>7.4412000000000003</v>
       </c>
       <c r="D276" t="s">
-        <v>39</v>
+        <v>535</v>
       </c>
       <c r="E276" s="2">
         <v>46141</v>
@@ -20592,16 +20639,16 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>180</v>
+        <v>436</v>
       </c>
       <c r="B277">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C277">
-        <v>6.7732000000000001</v>
+        <v>10.931699999999999</v>
       </c>
       <c r="D277" t="s">
-        <v>39</v>
+        <v>535</v>
       </c>
       <c r="E277" s="2">
         <v>46141</v>
@@ -20609,16 +20656,16 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>208</v>
+        <v>452</v>
       </c>
       <c r="B278">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C278">
-        <v>20.435300000000002</v>
+        <v>7.4935999999999998</v>
       </c>
       <c r="D278" t="s">
-        <v>39</v>
+        <v>535</v>
       </c>
       <c r="E278" s="2">
         <v>46141</v>
@@ -20626,16 +20673,16 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>210</v>
+        <v>468</v>
       </c>
       <c r="B279">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C279">
-        <v>20.806699999999999</v>
+        <v>8.2263000000000002</v>
       </c>
       <c r="D279" t="s">
-        <v>39</v>
+        <v>535</v>
       </c>
       <c r="E279" s="2">
         <v>46141</v>
@@ -20643,16 +20690,16 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>212</v>
+        <v>484</v>
       </c>
       <c r="B280">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C280">
-        <v>15.5441</v>
+        <v>9.5980000000000008</v>
       </c>
       <c r="D280" t="s">
-        <v>39</v>
+        <v>535</v>
       </c>
       <c r="E280" s="2">
         <v>46141</v>
@@ -20660,16 +20707,16 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>214</v>
+        <v>500</v>
       </c>
       <c r="B281">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="C281">
-        <v>22.4376</v>
+        <v>15.4183</v>
       </c>
       <c r="D281" t="s">
-        <v>39</v>
+        <v>535</v>
       </c>
       <c r="E281" s="2">
         <v>46141</v>
@@ -20677,13 +20724,16 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>760</v>
+        <v>516</v>
       </c>
       <c r="B282">
         <v>24</v>
       </c>
       <c r="C282">
-        <v>74.988399999999999</v>
+        <v>6.6531000000000002</v>
+      </c>
+      <c r="D282" t="s">
+        <v>535</v>
       </c>
       <c r="E282" s="2">
         <v>46141</v>
@@ -20691,16 +20741,13 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>450</v>
+        <v>760</v>
       </c>
       <c r="B283">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C283">
-        <v>7.5002000000000004</v>
-      </c>
-      <c r="D283" t="s">
-        <v>535</v>
+        <v>74.984300000000005</v>
       </c>
       <c r="E283" s="2">
         <v>46141</v>
@@ -20708,13 +20755,13 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>482</v>
+        <v>437</v>
       </c>
       <c r="B284">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C284">
-        <v>6.1449999999999996</v>
+        <v>17.4068</v>
       </c>
       <c r="D284" t="s">
         <v>535</v>
@@ -20725,13 +20772,13 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>498</v>
+        <v>453</v>
       </c>
       <c r="B285">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="C285">
-        <v>5.9164000000000003</v>
+        <v>13.967499999999999</v>
       </c>
       <c r="D285" t="s">
         <v>535</v>
@@ -20742,16 +20789,13 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>514</v>
+        <v>760</v>
       </c>
       <c r="B286">
         <v>24</v>
       </c>
       <c r="C286">
-        <v>6.3282999999999996</v>
-      </c>
-      <c r="D286" t="s">
-        <v>535</v>
+        <v>74.986400000000003</v>
       </c>
       <c r="E286" s="2">
         <v>46141</v>
@@ -20759,13 +20803,13 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="B287">
         <v>24</v>
       </c>
       <c r="C287">
-        <v>5.2625999999999999</v>
+        <v>10.6432</v>
       </c>
       <c r="D287" t="s">
         <v>535</v>
@@ -20776,13 +20820,13 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="B288">
         <v>24</v>
       </c>
       <c r="C288">
-        <v>9.2093000000000007</v>
+        <v>7.0914999999999999</v>
       </c>
       <c r="D288" t="s">
         <v>535</v>
@@ -20793,13 +20837,13 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B289">
         <v>24</v>
       </c>
       <c r="C289">
-        <v>6.3968999999999996</v>
+        <v>9.3945000000000007</v>
       </c>
       <c r="D289" t="s">
         <v>535</v>
@@ -20810,13 +20854,13 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B290">
         <v>24</v>
       </c>
       <c r="C290">
-        <v>7.4412000000000003</v>
+        <v>7.7038000000000002</v>
       </c>
       <c r="D290" t="s">
         <v>535</v>
@@ -20827,16 +20871,13 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>436</v>
+        <v>760</v>
       </c>
       <c r="B291">
         <v>24</v>
       </c>
       <c r="C291">
-        <v>10.931699999999999</v>
-      </c>
-      <c r="D291" t="s">
-        <v>535</v>
+        <v>74.984200000000001</v>
       </c>
       <c r="E291" s="2">
         <v>46141</v>
@@ -20844,16 +20885,13 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>452</v>
+        <v>760</v>
       </c>
       <c r="B292">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C292">
-        <v>7.4935999999999998</v>
-      </c>
-      <c r="D292" t="s">
-        <v>535</v>
+        <v>74.983199999999997</v>
       </c>
       <c r="E292" s="2">
         <v>46141</v>
@@ -20861,16 +20899,16 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>468</v>
+        <v>224</v>
       </c>
       <c r="B293">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C293">
-        <v>8.2263000000000002</v>
+        <v>10.6105</v>
       </c>
       <c r="D293" t="s">
-        <v>535</v>
+        <v>715</v>
       </c>
       <c r="E293" s="2">
         <v>46141</v>
@@ -20878,16 +20916,16 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>484</v>
+        <v>714</v>
       </c>
       <c r="B294">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C294">
-        <v>9.5980000000000008</v>
+        <v>7.7708000000000004</v>
       </c>
       <c r="D294" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="E294" s="2">
         <v>46141</v>
@@ -20895,16 +20933,16 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>500</v>
+        <v>713</v>
       </c>
       <c r="B295">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C295">
-        <v>15.4183</v>
+        <v>15.0802</v>
       </c>
       <c r="D295" t="s">
-        <v>535</v>
+        <v>710</v>
       </c>
       <c r="E295" s="2">
         <v>46141</v>
@@ -20912,16 +20950,16 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B296">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C296">
-        <v>6.6531000000000002</v>
+        <v>8.5643999999999991</v>
       </c>
       <c r="D296" t="s">
-        <v>535</v>
+        <v>520</v>
       </c>
       <c r="E296" s="2">
         <v>46141</v>
@@ -20929,13 +20967,16 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>760</v>
+        <v>706</v>
       </c>
       <c r="B297">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="C297">
-        <v>74.984300000000005</v>
+        <v>8.5068000000000001</v>
+      </c>
+      <c r="D297" t="s">
+        <v>705</v>
       </c>
       <c r="E297" s="2">
         <v>46141</v>
@@ -20943,16 +20984,16 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>437</v>
+        <v>333</v>
       </c>
       <c r="B298">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="C298">
-        <v>17.4068</v>
+        <v>8.5032999999999994</v>
       </c>
       <c r="D298" t="s">
-        <v>535</v>
+        <v>334</v>
       </c>
       <c r="E298" s="2">
         <v>46141</v>
@@ -20960,16 +21001,16 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>453</v>
+        <v>704</v>
       </c>
       <c r="B299">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="C299">
-        <v>13.967499999999999</v>
+        <v>6.5064000000000002</v>
       </c>
       <c r="D299" t="s">
-        <v>535</v>
+        <v>705</v>
       </c>
       <c r="E299" s="2">
         <v>46141</v>
@@ -20977,13 +21018,16 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>760</v>
+        <v>503</v>
       </c>
       <c r="B300">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C300">
-        <v>74.986400000000003</v>
+        <v>9.2588000000000008</v>
+      </c>
+      <c r="D300" t="s">
+        <v>419</v>
       </c>
       <c r="E300" s="2">
         <v>46141</v>
@@ -20991,16 +21035,13 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>469</v>
+        <v>760</v>
       </c>
       <c r="B301">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C301">
-        <v>10.6432</v>
-      </c>
-      <c r="D301" t="s">
-        <v>535</v>
+        <v>74.9863</v>
       </c>
       <c r="E301" s="2">
         <v>46141</v>
@@ -21008,301 +21049,3465 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>485</v>
-      </c>
-      <c r="B302">
-        <v>24</v>
-      </c>
-      <c r="C302">
-        <v>7.0914999999999999</v>
+        <v>321</v>
       </c>
       <c r="D302" t="s">
-        <v>535</v>
-      </c>
-      <c r="E302" s="2">
-        <v>46141</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="E302" s="2"/>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>501</v>
-      </c>
-      <c r="B303">
-        <v>24</v>
-      </c>
-      <c r="C303">
-        <v>9.3945000000000007</v>
+        <v>771</v>
       </c>
       <c r="D303" t="s">
-        <v>535</v>
-      </c>
-      <c r="E303" s="2">
-        <v>46141</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="E303" s="2"/>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>517</v>
-      </c>
-      <c r="B304">
-        <v>24</v>
-      </c>
-      <c r="C304">
-        <v>7.7038000000000002</v>
+        <v>426</v>
       </c>
       <c r="D304" t="s">
-        <v>535</v>
-      </c>
-      <c r="E304" s="2">
-        <v>46141</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="E304" s="2"/>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>760</v>
-      </c>
-      <c r="B305">
-        <v>24</v>
-      </c>
-      <c r="C305">
-        <v>74.984200000000001</v>
-      </c>
-      <c r="E305" s="2">
-        <v>46141</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="D305" t="s">
+        <v>218</v>
+      </c>
+      <c r="E305" s="2"/>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>760</v>
-      </c>
-      <c r="B306">
-        <v>23.9</v>
-      </c>
-      <c r="C306">
-        <v>74.983199999999997</v>
-      </c>
-      <c r="E306" s="2">
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A307" t="s">
-        <v>224</v>
-      </c>
-      <c r="B307">
-        <v>23.9</v>
-      </c>
-      <c r="C307">
-        <v>10.6105</v>
-      </c>
-      <c r="D307" t="s">
-        <v>715</v>
-      </c>
-      <c r="E307" s="2">
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A308" t="s">
-        <v>714</v>
-      </c>
-      <c r="B308">
-        <v>23.9</v>
-      </c>
-      <c r="C308">
-        <v>7.7708000000000004</v>
-      </c>
-      <c r="D308" t="s">
-        <v>530</v>
-      </c>
-      <c r="E308" s="2">
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A309" t="s">
-        <v>713</v>
-      </c>
-      <c r="B309">
-        <v>23.9</v>
-      </c>
-      <c r="C309">
-        <v>15.0802</v>
-      </c>
-      <c r="D309" t="s">
-        <v>710</v>
-      </c>
-      <c r="E309" s="2">
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A310" t="s">
-        <v>521</v>
-      </c>
-      <c r="B310">
-        <v>23.9</v>
-      </c>
-      <c r="C310">
-        <v>8.5643999999999991</v>
-      </c>
-      <c r="D310" t="s">
-        <v>520</v>
-      </c>
-      <c r="E310" s="2">
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A311" t="s">
-        <v>706</v>
-      </c>
-      <c r="B311">
-        <v>23.9</v>
-      </c>
-      <c r="C311">
-        <v>8.5068000000000001</v>
-      </c>
-      <c r="D311" t="s">
-        <v>705</v>
-      </c>
-      <c r="E311" s="2">
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A312" t="s">
-        <v>333</v>
-      </c>
-      <c r="B312">
-        <v>23.9</v>
-      </c>
-      <c r="C312">
-        <v>8.5032999999999994</v>
-      </c>
-      <c r="D312" t="s">
-        <v>334</v>
-      </c>
-      <c r="E312" s="2">
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A313" t="s">
-        <v>704</v>
-      </c>
-      <c r="B313">
-        <v>23.9</v>
-      </c>
-      <c r="C313">
-        <v>6.5064000000000002</v>
-      </c>
-      <c r="D313" t="s">
-        <v>705</v>
-      </c>
-      <c r="E313" s="2">
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A314" t="s">
-        <v>503</v>
-      </c>
-      <c r="B314">
-        <v>23.9</v>
-      </c>
-      <c r="C314">
-        <v>9.2588000000000008</v>
-      </c>
-      <c r="D314" t="s">
-        <v>419</v>
-      </c>
-      <c r="E314" s="2">
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A315" t="s">
-        <v>760</v>
-      </c>
-      <c r="B315">
-        <v>23.9</v>
-      </c>
-      <c r="C315">
-        <v>74.9863</v>
-      </c>
-      <c r="E315" s="2">
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A316" t="s">
-        <v>321</v>
-      </c>
-      <c r="D316" t="s">
-        <v>319</v>
-      </c>
-      <c r="E316" s="2">
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A317" t="s">
-        <v>536</v>
-      </c>
-      <c r="D317" t="s">
-        <v>720</v>
-      </c>
-      <c r="E317" s="2">
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A318" t="s">
-        <v>771</v>
-      </c>
-      <c r="D318" t="s">
-        <v>233</v>
-      </c>
-      <c r="E318" s="2">
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A319" t="s">
-        <v>426</v>
-      </c>
-      <c r="D319" t="s">
-        <v>424</v>
-      </c>
-      <c r="E319" s="2">
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A320" t="s">
-        <v>238</v>
-      </c>
-      <c r="D320" t="s">
-        <v>218</v>
-      </c>
-      <c r="E320" s="2">
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A321" t="s">
         <v>723</v>
       </c>
-      <c r="D321" t="s">
+      <c r="D306" t="s">
         <v>434</v>
       </c>
-      <c r="E321" s="2">
-        <v>46141</v>
-      </c>
+      <c r="E306" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1E5B39D-5383-45F0-B944-95C8218437E5}">
+  <dimension ref="A1:J302"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B1" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B5" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>390</v>
+      </c>
+      <c r="B6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>406</v>
+      </c>
+      <c r="B7" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>325</v>
+      </c>
+      <c r="B8" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>343</v>
+      </c>
+      <c r="B9" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>359</v>
+      </c>
+      <c r="B10" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>375</v>
+      </c>
+      <c r="B11" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>391</v>
+      </c>
+      <c r="B12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>407</v>
+      </c>
+      <c r="B13" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>326</v>
+      </c>
+      <c r="B14" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>344</v>
+      </c>
+      <c r="B15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>360</v>
+      </c>
+      <c r="B16" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>376</v>
+      </c>
+      <c r="B17" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>392</v>
+      </c>
+      <c r="B18" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>408</v>
+      </c>
+      <c r="B19" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>327</v>
+      </c>
+      <c r="B20" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>345</v>
+      </c>
+      <c r="B21" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>361</v>
+      </c>
+      <c r="B22" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>377</v>
+      </c>
+      <c r="B23" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>393</v>
+      </c>
+      <c r="B24" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>409</v>
+      </c>
+      <c r="B25" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>418</v>
+      </c>
+      <c r="B26" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>438</v>
+      </c>
+      <c r="B27" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>454</v>
+      </c>
+      <c r="B28" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>470</v>
+      </c>
+      <c r="B29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B30" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>502</v>
+      </c>
+      <c r="B31" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B32" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>439</v>
+      </c>
+      <c r="B33" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>455</v>
+      </c>
+      <c r="B34" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>471</v>
+      </c>
+      <c r="B35" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>487</v>
+      </c>
+      <c r="B36" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>503</v>
+      </c>
+      <c r="B37" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>421</v>
+      </c>
+      <c r="B38" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>440</v>
+      </c>
+      <c r="B39" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>456</v>
+      </c>
+      <c r="B40" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>472</v>
+      </c>
+      <c r="B41" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>488</v>
+      </c>
+      <c r="B42" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>504</v>
+      </c>
+      <c r="B43" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>422</v>
+      </c>
+      <c r="B44" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>441</v>
+      </c>
+      <c r="B45" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>457</v>
+      </c>
+      <c r="B46" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>489</v>
+      </c>
+      <c r="B48" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>505</v>
+      </c>
+      <c r="B49" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>717</v>
+      </c>
+      <c r="B50" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>721</v>
+      </c>
+      <c r="B52" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B53" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>723</v>
+      </c>
+      <c r="B54" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>521</v>
+      </c>
+      <c r="B56" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>522</v>
+      </c>
+      <c r="B57" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>523</v>
+      </c>
+      <c r="B58" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>37</v>
+      </c>
+      <c r="B59" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>42</v>
+      </c>
+      <c r="B61" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>76</v>
+      </c>
+      <c r="B65" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>78</v>
+      </c>
+      <c r="B66" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>106</v>
+      </c>
+      <c r="B67" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>108</v>
+      </c>
+      <c r="B68" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>110</v>
+      </c>
+      <c r="B69" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>112</v>
+      </c>
+      <c r="B70" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>140</v>
+      </c>
+      <c r="B71" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>142</v>
+      </c>
+      <c r="B72" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>144</v>
+      </c>
+      <c r="B73" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>146</v>
+      </c>
+      <c r="B74" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>174</v>
+      </c>
+      <c r="B75" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B76" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>178</v>
+      </c>
+      <c r="B77" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>180</v>
+      </c>
+      <c r="B78" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>208</v>
+      </c>
+      <c r="B79" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>210</v>
+      </c>
+      <c r="B80" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>212</v>
+      </c>
+      <c r="B81" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>214</v>
+      </c>
+      <c r="B82" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B83" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>450</v>
+      </c>
+      <c r="B84" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>482</v>
+      </c>
+      <c r="B86" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>498</v>
+      </c>
+      <c r="B87" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>514</v>
+      </c>
+      <c r="B88" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>451</v>
+      </c>
+      <c r="B90" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>467</v>
+      </c>
+      <c r="B91" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>499</v>
+      </c>
+      <c r="B93" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>515</v>
+      </c>
+      <c r="B94" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>436</v>
+      </c>
+      <c r="B95" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>452</v>
+      </c>
+      <c r="B96" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>468</v>
+      </c>
+      <c r="B97" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>484</v>
+      </c>
+      <c r="B98" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>500</v>
+      </c>
+      <c r="B99" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>516</v>
+      </c>
+      <c r="B100" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>437</v>
+      </c>
+      <c r="B101" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>453</v>
+      </c>
+      <c r="B102" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>469</v>
+      </c>
+      <c r="B103" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>485</v>
+      </c>
+      <c r="B104" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>501</v>
+      </c>
+      <c r="B105" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>517</v>
+      </c>
+      <c r="B106" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>714</v>
+      </c>
+      <c r="B107" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>717</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>718</v>
+      </c>
+      <c r="B110" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>704</v>
+      </c>
+      <c r="B111" t="s">
+        <v>705</v>
+      </c>
+      <c r="H111" t="s">
+        <v>704</v>
+      </c>
+      <c r="J111" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>706</v>
+      </c>
+      <c r="B112" t="s">
+        <v>705</v>
+      </c>
+      <c r="H112" t="s">
+        <v>706</v>
+      </c>
+      <c r="J112" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A113" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="H113" t="s">
+        <v>707</v>
+      </c>
+      <c r="J113" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>333</v>
+      </c>
+      <c r="B114" t="s">
+        <v>334</v>
+      </c>
+      <c r="H114" t="s">
+        <v>708</v>
+      </c>
+      <c r="J114" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>337</v>
+      </c>
+      <c r="B115" t="s">
+        <v>334</v>
+      </c>
+      <c r="H115" t="s">
+        <v>724</v>
+      </c>
+      <c r="J115" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H116" t="s">
+        <v>727</v>
+      </c>
+      <c r="J116" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>771</v>
+      </c>
+      <c r="B117" t="s">
+        <v>233</v>
+      </c>
+      <c r="H117" t="s">
+        <v>729</v>
+      </c>
+      <c r="J117" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H118" t="s">
+        <v>731</v>
+      </c>
+      <c r="J118" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A119" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="B119" t="s">
+        <v>233</v>
+      </c>
+      <c r="H119" t="s">
+        <v>572</v>
+      </c>
+      <c r="J119" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>7</v>
+      </c>
+      <c r="B120" t="s">
+        <v>12</v>
+      </c>
+      <c r="H120" t="s">
+        <v>575</v>
+      </c>
+      <c r="J120" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>13</v>
+      </c>
+      <c r="B121" t="s">
+        <v>12</v>
+      </c>
+      <c r="C121" t="s">
+        <v>773</v>
+      </c>
+      <c r="H121" t="s">
+        <v>577</v>
+      </c>
+      <c r="J121" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H122" t="s">
+        <v>579</v>
+      </c>
+      <c r="J122" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>17</v>
+      </c>
+      <c r="B123" t="s">
+        <v>12</v>
+      </c>
+      <c r="H123" t="s">
+        <v>605</v>
+      </c>
+      <c r="J123" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>46</v>
+      </c>
+      <c r="B124" t="s">
+        <v>12</v>
+      </c>
+      <c r="H124" t="s">
+        <v>608</v>
+      </c>
+      <c r="J124" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A125" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B125" t="s">
+        <v>12</v>
+      </c>
+      <c r="H125" t="s">
+        <v>610</v>
+      </c>
+      <c r="J125" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>52</v>
+      </c>
+      <c r="B126" t="s">
+        <v>12</v>
+      </c>
+      <c r="H126" t="s">
+        <v>612</v>
+      </c>
+      <c r="J126" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H127" t="s">
+        <v>638</v>
+      </c>
+      <c r="J127" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>80</v>
+      </c>
+      <c r="B128" t="s">
+        <v>12</v>
+      </c>
+      <c r="H128" t="s">
+        <v>641</v>
+      </c>
+      <c r="J128" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>84</v>
+      </c>
+      <c r="B129" t="s">
+        <v>12</v>
+      </c>
+      <c r="H129" t="s">
+        <v>643</v>
+      </c>
+      <c r="J129" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>86</v>
+      </c>
+      <c r="B130" t="s">
+        <v>12</v>
+      </c>
+      <c r="H130" t="s">
+        <v>645</v>
+      </c>
+      <c r="J130" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>88</v>
+      </c>
+      <c r="B131" t="s">
+        <v>12</v>
+      </c>
+      <c r="H131" t="s">
+        <v>671</v>
+      </c>
+      <c r="J131" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>114</v>
+      </c>
+      <c r="B132" t="s">
+        <v>12</v>
+      </c>
+      <c r="H132" t="s">
+        <v>674</v>
+      </c>
+      <c r="J132" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>118</v>
+      </c>
+      <c r="B133" t="s">
+        <v>12</v>
+      </c>
+      <c r="H133" t="s">
+        <v>676</v>
+      </c>
+      <c r="J133" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>120</v>
+      </c>
+      <c r="B134" t="s">
+        <v>12</v>
+      </c>
+      <c r="H134" t="s">
+        <v>678</v>
+      </c>
+      <c r="J134" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>122</v>
+      </c>
+      <c r="B135" t="s">
+        <v>12</v>
+      </c>
+      <c r="H135" t="s">
+        <v>333</v>
+      </c>
+      <c r="J135" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>148</v>
+      </c>
+      <c r="B136" t="s">
+        <v>12</v>
+      </c>
+      <c r="H136" t="s">
+        <v>350</v>
+      </c>
+      <c r="J136" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>152</v>
+      </c>
+      <c r="B137" t="s">
+        <v>12</v>
+      </c>
+      <c r="H137" t="s">
+        <v>366</v>
+      </c>
+      <c r="J137" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>154</v>
+      </c>
+      <c r="B138" t="s">
+        <v>12</v>
+      </c>
+      <c r="H138" t="s">
+        <v>382</v>
+      </c>
+      <c r="J138" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>156</v>
+      </c>
+      <c r="B139" t="s">
+        <v>12</v>
+      </c>
+      <c r="H139" t="s">
+        <v>398</v>
+      </c>
+      <c r="J139" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>182</v>
+      </c>
+      <c r="B140" t="s">
+        <v>12</v>
+      </c>
+      <c r="H140" t="s">
+        <v>414</v>
+      </c>
+      <c r="J140" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>186</v>
+      </c>
+      <c r="B141" t="s">
+        <v>12</v>
+      </c>
+      <c r="H141" t="s">
+        <v>335</v>
+      </c>
+      <c r="J141" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>188</v>
+      </c>
+      <c r="B142" t="s">
+        <v>12</v>
+      </c>
+      <c r="H142" t="s">
+        <v>351</v>
+      </c>
+      <c r="J142" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>190</v>
+      </c>
+      <c r="B143" t="s">
+        <v>12</v>
+      </c>
+      <c r="H143" t="s">
+        <v>367</v>
+      </c>
+      <c r="J143" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>320</v>
+      </c>
+      <c r="B144" t="s">
+        <v>319</v>
+      </c>
+      <c r="H144" t="s">
+        <v>383</v>
+      </c>
+      <c r="J144" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>321</v>
+      </c>
+      <c r="B145" t="s">
+        <v>319</v>
+      </c>
+      <c r="H145" t="s">
+        <v>399</v>
+      </c>
+      <c r="J145" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A146" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B146" t="s">
+        <v>319</v>
+      </c>
+      <c r="H146" t="s">
+        <v>415</v>
+      </c>
+      <c r="J146" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>423</v>
+      </c>
+      <c r="B147" t="s">
+        <v>424</v>
+      </c>
+      <c r="H147" t="s">
+        <v>336</v>
+      </c>
+      <c r="J147" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>426</v>
+      </c>
+      <c r="B148" t="s">
+        <v>424</v>
+      </c>
+      <c r="H148" t="s">
+        <v>352</v>
+      </c>
+      <c r="J148" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A149" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="H149" t="s">
+        <v>368</v>
+      </c>
+      <c r="J149" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>761</v>
+      </c>
+      <c r="B150" t="s">
+        <v>223</v>
+      </c>
+      <c r="H150" t="s">
+        <v>384</v>
+      </c>
+      <c r="J150" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>770</v>
+      </c>
+      <c r="B151" t="s">
+        <v>223</v>
+      </c>
+      <c r="H151" t="s">
+        <v>400</v>
+      </c>
+      <c r="J151" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A152" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B152" t="s">
+        <v>223</v>
+      </c>
+      <c r="H152" t="s">
+        <v>416</v>
+      </c>
+      <c r="J152" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A153" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="H153" t="s">
+        <v>337</v>
+      </c>
+      <c r="J153" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A154" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="H154" t="s">
+        <v>353</v>
+      </c>
+      <c r="J154" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>224</v>
+      </c>
+      <c r="B155" t="s">
+        <v>715</v>
+      </c>
+      <c r="H155" t="s">
+        <v>369</v>
+      </c>
+      <c r="J155" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A156" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B156" t="s">
+        <v>715</v>
+      </c>
+      <c r="H156" t="s">
+        <v>385</v>
+      </c>
+      <c r="J156" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A157" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="H157" t="s">
+        <v>401</v>
+      </c>
+      <c r="J157" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>243</v>
+      </c>
+      <c r="B158" t="s">
+        <v>715</v>
+      </c>
+      <c r="H158" t="s">
+        <v>417</v>
+      </c>
+      <c r="J158" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>244</v>
+      </c>
+      <c r="B159" t="s">
+        <v>715</v>
+      </c>
+      <c r="H159" t="s">
+        <v>232</v>
+      </c>
+      <c r="J159" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>31</v>
+      </c>
+      <c r="B160" t="s">
+        <v>30</v>
+      </c>
+      <c r="H160" t="s">
+        <v>281</v>
+      </c>
+      <c r="J160" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A161" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H161" t="s">
+        <v>234</v>
+      </c>
+      <c r="J161" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A162" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H162" t="s">
+        <v>282</v>
+      </c>
+      <c r="J162" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A163" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H163" t="s">
+        <v>235</v>
+      </c>
+      <c r="J163" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A164" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H164" t="s">
+        <v>283</v>
+      </c>
+      <c r="J164" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>446</v>
+      </c>
+      <c r="B165" t="s">
+        <v>329</v>
+      </c>
+      <c r="H165" t="s">
+        <v>236</v>
+      </c>
+      <c r="J165" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>462</v>
+      </c>
+      <c r="B166" t="s">
+        <v>329</v>
+      </c>
+      <c r="H166" t="s">
+        <v>284</v>
+      </c>
+      <c r="J166" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>478</v>
+      </c>
+      <c r="B167" t="s">
+        <v>329</v>
+      </c>
+      <c r="H167" t="s">
+        <v>249</v>
+      </c>
+      <c r="J167" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>494</v>
+      </c>
+      <c r="B168" t="s">
+        <v>329</v>
+      </c>
+      <c r="H168" t="s">
+        <v>297</v>
+      </c>
+      <c r="J168" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>510</v>
+      </c>
+      <c r="B169" t="s">
+        <v>329</v>
+      </c>
+      <c r="H169" t="s">
+        <v>250</v>
+      </c>
+      <c r="J169" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>430</v>
+      </c>
+      <c r="B170" t="s">
+        <v>329</v>
+      </c>
+      <c r="H170" t="s">
+        <v>298</v>
+      </c>
+      <c r="J170" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>447</v>
+      </c>
+      <c r="B171" t="s">
+        <v>329</v>
+      </c>
+      <c r="H171" t="s">
+        <v>251</v>
+      </c>
+      <c r="J171" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>463</v>
+      </c>
+      <c r="B172" t="s">
+        <v>329</v>
+      </c>
+      <c r="H172" t="s">
+        <v>299</v>
+      </c>
+      <c r="J172" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>479</v>
+      </c>
+      <c r="B173" t="s">
+        <v>329</v>
+      </c>
+      <c r="H173" t="s">
+        <v>252</v>
+      </c>
+      <c r="J173" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>495</v>
+      </c>
+      <c r="B174" t="s">
+        <v>329</v>
+      </c>
+      <c r="H174" t="s">
+        <v>300</v>
+      </c>
+      <c r="J174" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>511</v>
+      </c>
+      <c r="B175" t="s">
+        <v>329</v>
+      </c>
+      <c r="H175" t="s">
+        <v>265</v>
+      </c>
+      <c r="J175" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>431</v>
+      </c>
+      <c r="B176" t="s">
+        <v>329</v>
+      </c>
+      <c r="H176" t="s">
+        <v>313</v>
+      </c>
+      <c r="J176" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>448</v>
+      </c>
+      <c r="B177" t="s">
+        <v>329</v>
+      </c>
+      <c r="H177" t="s">
+        <v>266</v>
+      </c>
+      <c r="J177" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>464</v>
+      </c>
+      <c r="B178" t="s">
+        <v>329</v>
+      </c>
+      <c r="H178" t="s">
+        <v>314</v>
+      </c>
+      <c r="J178" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>480</v>
+      </c>
+      <c r="B179" t="s">
+        <v>329</v>
+      </c>
+      <c r="H179" t="s">
+        <v>267</v>
+      </c>
+      <c r="J179" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>496</v>
+      </c>
+      <c r="B180" t="s">
+        <v>329</v>
+      </c>
+      <c r="H180" t="s">
+        <v>315</v>
+      </c>
+      <c r="J180" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>512</v>
+      </c>
+      <c r="B181" t="s">
+        <v>329</v>
+      </c>
+      <c r="H181" t="s">
+        <v>268</v>
+      </c>
+      <c r="J181" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>432</v>
+      </c>
+      <c r="B182" t="s">
+        <v>329</v>
+      </c>
+      <c r="H182" t="s">
+        <v>316</v>
+      </c>
+      <c r="J182" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>449</v>
+      </c>
+      <c r="B183" t="s">
+        <v>329</v>
+      </c>
+      <c r="H183" t="s">
+        <v>317</v>
+      </c>
+      <c r="J183" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>465</v>
+      </c>
+      <c r="B184" t="s">
+        <v>329</v>
+      </c>
+      <c r="H184" t="s">
+        <v>338</v>
+      </c>
+      <c r="J184" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>481</v>
+      </c>
+      <c r="B185" t="s">
+        <v>329</v>
+      </c>
+      <c r="H185" t="s">
+        <v>354</v>
+      </c>
+      <c r="J185" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>497</v>
+      </c>
+      <c r="B186" t="s">
+        <v>329</v>
+      </c>
+      <c r="H186" t="s">
+        <v>370</v>
+      </c>
+      <c r="J186" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>513</v>
+      </c>
+      <c r="B187" t="s">
+        <v>329</v>
+      </c>
+      <c r="H187" t="s">
+        <v>386</v>
+      </c>
+      <c r="J187" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>534</v>
+      </c>
+      <c r="B188" t="s">
+        <v>720</v>
+      </c>
+      <c r="H188" t="s">
+        <v>402</v>
+      </c>
+      <c r="J188" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>536</v>
+      </c>
+      <c r="B189" t="s">
+        <v>720</v>
+      </c>
+      <c r="H189" t="s">
+        <v>320</v>
+      </c>
+      <c r="J189" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A190" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="H190" t="s">
+        <v>339</v>
+      </c>
+      <c r="J190" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A191" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="H191" t="s">
+        <v>355</v>
+      </c>
+      <c r="J191" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>227</v>
+      </c>
+      <c r="B192" t="s">
+        <v>228</v>
+      </c>
+      <c r="H192" t="s">
+        <v>371</v>
+      </c>
+      <c r="J192" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>277</v>
+      </c>
+      <c r="B193" t="s">
+        <v>228</v>
+      </c>
+      <c r="H193" t="s">
+        <v>387</v>
+      </c>
+      <c r="J193" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>229</v>
+      </c>
+      <c r="B194" t="s">
+        <v>228</v>
+      </c>
+      <c r="H194" t="s">
+        <v>403</v>
+      </c>
+      <c r="J194" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>230</v>
+      </c>
+      <c r="B195" t="s">
+        <v>228</v>
+      </c>
+      <c r="H195" t="s">
+        <v>321</v>
+      </c>
+      <c r="J195" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>279</v>
+      </c>
+      <c r="B196" t="s">
+        <v>228</v>
+      </c>
+      <c r="H196" t="s">
+        <v>340</v>
+      </c>
+      <c r="J196" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>231</v>
+      </c>
+      <c r="B197" t="s">
+        <v>228</v>
+      </c>
+      <c r="H197" t="s">
+        <v>356</v>
+      </c>
+      <c r="J197" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A198" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H198" t="s">
+        <v>372</v>
+      </c>
+      <c r="J198" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>280</v>
+      </c>
+      <c r="B199" t="s">
+        <v>228</v>
+      </c>
+      <c r="H199" t="s">
+        <v>388</v>
+      </c>
+      <c r="J199" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>245</v>
+      </c>
+      <c r="B200" t="s">
+        <v>228</v>
+      </c>
+      <c r="H200" t="s">
+        <v>404</v>
+      </c>
+      <c r="J200" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>293</v>
+      </c>
+      <c r="B201" t="s">
+        <v>228</v>
+      </c>
+      <c r="H201" t="s">
+        <v>322</v>
+      </c>
+      <c r="J201" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A202" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H202" t="s">
+        <v>341</v>
+      </c>
+      <c r="J202" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>294</v>
+      </c>
+      <c r="B203" t="s">
+        <v>228</v>
+      </c>
+      <c r="H203" t="s">
+        <v>357</v>
+      </c>
+      <c r="J203" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>247</v>
+      </c>
+      <c r="B204" t="s">
+        <v>228</v>
+      </c>
+      <c r="H204" t="s">
+        <v>373</v>
+      </c>
+      <c r="J204" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>295</v>
+      </c>
+      <c r="B205" t="s">
+        <v>228</v>
+      </c>
+      <c r="H205" t="s">
+        <v>389</v>
+      </c>
+      <c r="J205" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>248</v>
+      </c>
+      <c r="B206" t="s">
+        <v>228</v>
+      </c>
+      <c r="H206" t="s">
+        <v>405</v>
+      </c>
+      <c r="J206" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>296</v>
+      </c>
+      <c r="B207" t="s">
+        <v>228</v>
+      </c>
+      <c r="H207" t="s">
+        <v>423</v>
+      </c>
+      <c r="J207" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>261</v>
+      </c>
+      <c r="B208" t="s">
+        <v>228</v>
+      </c>
+      <c r="H208" t="s">
+        <v>442</v>
+      </c>
+      <c r="J208" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>309</v>
+      </c>
+      <c r="B209" t="s">
+        <v>228</v>
+      </c>
+      <c r="H209" t="s">
+        <v>458</v>
+      </c>
+      <c r="J209" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>262</v>
+      </c>
+      <c r="B210" t="s">
+        <v>228</v>
+      </c>
+      <c r="H210" t="s">
+        <v>474</v>
+      </c>
+      <c r="J210" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>310</v>
+      </c>
+      <c r="B211" t="s">
+        <v>228</v>
+      </c>
+      <c r="H211" t="s">
+        <v>490</v>
+      </c>
+      <c r="J211" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>263</v>
+      </c>
+      <c r="B212" t="s">
+        <v>228</v>
+      </c>
+      <c r="H212" t="s">
+        <v>506</v>
+      </c>
+      <c r="J212" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>311</v>
+      </c>
+      <c r="B213" t="s">
+        <v>228</v>
+      </c>
+      <c r="H213" t="s">
+        <v>425</v>
+      </c>
+      <c r="J213" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>264</v>
+      </c>
+      <c r="B214" t="s">
+        <v>228</v>
+      </c>
+      <c r="H214" t="s">
+        <v>443</v>
+      </c>
+      <c r="J214" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>312</v>
+      </c>
+      <c r="B215" t="s">
+        <v>228</v>
+      </c>
+      <c r="H215" t="s">
+        <v>459</v>
+      </c>
+      <c r="J215" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>328</v>
+      </c>
+      <c r="B216" t="s">
+        <v>429</v>
+      </c>
+      <c r="H216" t="s">
+        <v>475</v>
+      </c>
+      <c r="J216" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>346</v>
+      </c>
+      <c r="B217" t="s">
+        <v>429</v>
+      </c>
+      <c r="H217" t="s">
+        <v>491</v>
+      </c>
+      <c r="J217" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>362</v>
+      </c>
+      <c r="B218" t="s">
+        <v>429</v>
+      </c>
+      <c r="H218" t="s">
+        <v>507</v>
+      </c>
+      <c r="J218" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>378</v>
+      </c>
+      <c r="B219" t="s">
+        <v>429</v>
+      </c>
+      <c r="H219" t="s">
+        <v>426</v>
+      </c>
+      <c r="J219" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>394</v>
+      </c>
+      <c r="B220" t="s">
+        <v>429</v>
+      </c>
+      <c r="H220" t="s">
+        <v>444</v>
+      </c>
+      <c r="J220" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>410</v>
+      </c>
+      <c r="B221" t="s">
+        <v>429</v>
+      </c>
+      <c r="H221" t="s">
+        <v>460</v>
+      </c>
+      <c r="J221" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>330</v>
+      </c>
+      <c r="B222" t="s">
+        <v>429</v>
+      </c>
+      <c r="H222" t="s">
+        <v>476</v>
+      </c>
+      <c r="J222" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>347</v>
+      </c>
+      <c r="B223" t="s">
+        <v>429</v>
+      </c>
+      <c r="H223" t="s">
+        <v>492</v>
+      </c>
+      <c r="J223" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>363</v>
+      </c>
+      <c r="B224" t="s">
+        <v>429</v>
+      </c>
+      <c r="H224" t="s">
+        <v>508</v>
+      </c>
+      <c r="J224" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>379</v>
+      </c>
+      <c r="B225" t="s">
+        <v>429</v>
+      </c>
+      <c r="H225" t="s">
+        <v>427</v>
+      </c>
+      <c r="J225" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>395</v>
+      </c>
+      <c r="B226" t="s">
+        <v>429</v>
+      </c>
+      <c r="H226" t="s">
+        <v>445</v>
+      </c>
+      <c r="J226" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>411</v>
+      </c>
+      <c r="B227" t="s">
+        <v>429</v>
+      </c>
+      <c r="H227" t="s">
+        <v>461</v>
+      </c>
+      <c r="J227" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>331</v>
+      </c>
+      <c r="B228" t="s">
+        <v>429</v>
+      </c>
+      <c r="H228" t="s">
+        <v>477</v>
+      </c>
+      <c r="J228" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>348</v>
+      </c>
+      <c r="B229" t="s">
+        <v>429</v>
+      </c>
+      <c r="H229" t="s">
+        <v>493</v>
+      </c>
+      <c r="J229" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>364</v>
+      </c>
+      <c r="B230" t="s">
+        <v>429</v>
+      </c>
+      <c r="H230" t="s">
+        <v>509</v>
+      </c>
+      <c r="J230" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>380</v>
+      </c>
+      <c r="B231" t="s">
+        <v>429</v>
+      </c>
+      <c r="H231" t="s">
+        <v>222</v>
+      </c>
+      <c r="J231" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>396</v>
+      </c>
+      <c r="B232" t="s">
+        <v>429</v>
+      </c>
+      <c r="H232" t="s">
+        <v>273</v>
+      </c>
+      <c r="J232" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>412</v>
+      </c>
+      <c r="B233" t="s">
+        <v>429</v>
+      </c>
+      <c r="H233" t="s">
+        <v>224</v>
+      </c>
+      <c r="J233" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>332</v>
+      </c>
+      <c r="B234" t="s">
+        <v>429</v>
+      </c>
+      <c r="H234" t="s">
+        <v>274</v>
+      </c>
+      <c r="J234" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>349</v>
+      </c>
+      <c r="B235" t="s">
+        <v>429</v>
+      </c>
+      <c r="H235" t="s">
+        <v>225</v>
+      </c>
+      <c r="J235" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>365</v>
+      </c>
+      <c r="B236" t="s">
+        <v>429</v>
+      </c>
+      <c r="H236" t="s">
+        <v>275</v>
+      </c>
+      <c r="J236" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>381</v>
+      </c>
+      <c r="B237" t="s">
+        <v>429</v>
+      </c>
+      <c r="H237" t="s">
+        <v>226</v>
+      </c>
+      <c r="J237" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>397</v>
+      </c>
+      <c r="B238" t="s">
+        <v>429</v>
+      </c>
+      <c r="H238" t="s">
+        <v>276</v>
+      </c>
+      <c r="J238" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>413</v>
+      </c>
+      <c r="B239" t="s">
+        <v>429</v>
+      </c>
+      <c r="H239" t="s">
+        <v>241</v>
+      </c>
+      <c r="J239" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>524</v>
+      </c>
+      <c r="B240" t="s">
+        <v>525</v>
+      </c>
+      <c r="H240" t="s">
+        <v>289</v>
+      </c>
+      <c r="J240" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>526</v>
+      </c>
+      <c r="B241" t="s">
+        <v>525</v>
+      </c>
+      <c r="H241" t="s">
+        <v>242</v>
+      </c>
+      <c r="J241" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>527</v>
+      </c>
+      <c r="B242" t="s">
+        <v>525</v>
+      </c>
+      <c r="H242" t="s">
+        <v>290</v>
+      </c>
+      <c r="J242" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>528</v>
+      </c>
+      <c r="B243" t="s">
+        <v>525</v>
+      </c>
+      <c r="H243" t="s">
+        <v>243</v>
+      </c>
+      <c r="J243" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>709</v>
+      </c>
+      <c r="B244" t="s">
+        <v>710</v>
+      </c>
+      <c r="H244" t="s">
+        <v>291</v>
+      </c>
+      <c r="J244" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>711</v>
+      </c>
+      <c r="B245" t="s">
+        <v>710</v>
+      </c>
+      <c r="H245" t="s">
+        <v>244</v>
+      </c>
+      <c r="J245" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A246" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B246" t="s">
+        <v>710</v>
+      </c>
+      <c r="H246" t="s">
+        <v>292</v>
+      </c>
+      <c r="J246" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>713</v>
+      </c>
+      <c r="B247" t="s">
+        <v>710</v>
+      </c>
+      <c r="H247" t="s">
+        <v>257</v>
+      </c>
+      <c r="J247" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>216</v>
+      </c>
+      <c r="B248" t="s">
+        <v>218</v>
+      </c>
+      <c r="H248" t="s">
+        <v>305</v>
+      </c>
+      <c r="J248" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>269</v>
+      </c>
+      <c r="B249" t="s">
+        <v>218</v>
+      </c>
+      <c r="H249" t="s">
+        <v>258</v>
+      </c>
+      <c r="J249" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>219</v>
+      </c>
+      <c r="B250" t="s">
+        <v>218</v>
+      </c>
+      <c r="H250" t="s">
+        <v>306</v>
+      </c>
+      <c r="J250" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>270</v>
+      </c>
+      <c r="B251" t="s">
+        <v>218</v>
+      </c>
+      <c r="H251" t="s">
+        <v>259</v>
+      </c>
+      <c r="J251" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>220</v>
+      </c>
+      <c r="B252" t="s">
+        <v>218</v>
+      </c>
+      <c r="H252" t="s">
+        <v>307</v>
+      </c>
+      <c r="J252" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>271</v>
+      </c>
+      <c r="B253" t="s">
+        <v>218</v>
+      </c>
+      <c r="H253" t="s">
+        <v>260</v>
+      </c>
+      <c r="J253" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>221</v>
+      </c>
+      <c r="B254" t="s">
+        <v>218</v>
+      </c>
+      <c r="H254" t="s">
+        <v>308</v>
+      </c>
+      <c r="J254" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>272</v>
+      </c>
+      <c r="B255" t="s">
+        <v>218</v>
+      </c>
+      <c r="H255" t="s">
+        <v>714</v>
+      </c>
+      <c r="J255" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>237</v>
+      </c>
+      <c r="B256" t="s">
+        <v>218</v>
+      </c>
+      <c r="H256" t="s">
+        <v>716</v>
+      </c>
+      <c r="J256" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>285</v>
+      </c>
+      <c r="B257" t="s">
+        <v>218</v>
+      </c>
+      <c r="H257" t="s">
+        <v>717</v>
+      </c>
+      <c r="J257" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>238</v>
+      </c>
+      <c r="B258" t="s">
+        <v>218</v>
+      </c>
+      <c r="H258" t="s">
+        <v>718</v>
+      </c>
+      <c r="J258" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>286</v>
+      </c>
+      <c r="B259" t="s">
+        <v>218</v>
+      </c>
+      <c r="H259" t="s">
+        <v>741</v>
+      </c>
+      <c r="J259" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A260" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="H260" t="s">
+        <v>743</v>
+      </c>
+      <c r="J260" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>287</v>
+      </c>
+      <c r="B261" t="s">
+        <v>218</v>
+      </c>
+      <c r="H261" t="s">
+        <v>745</v>
+      </c>
+      <c r="J261" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>240</v>
+      </c>
+      <c r="B262" t="s">
+        <v>218</v>
+      </c>
+      <c r="H262" t="s">
+        <v>747</v>
+      </c>
+      <c r="J262" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>288</v>
+      </c>
+      <c r="B263" t="s">
+        <v>218</v>
+      </c>
+      <c r="H263" t="s">
+        <v>589</v>
+      </c>
+      <c r="J263" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>253</v>
+      </c>
+      <c r="B264" t="s">
+        <v>218</v>
+      </c>
+      <c r="H264" t="s">
+        <v>591</v>
+      </c>
+      <c r="J264" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>301</v>
+      </c>
+      <c r="B265" t="s">
+        <v>218</v>
+      </c>
+      <c r="H265" t="s">
+        <v>593</v>
+      </c>
+      <c r="J265" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>254</v>
+      </c>
+      <c r="B266" t="s">
+        <v>218</v>
+      </c>
+      <c r="H266" t="s">
+        <v>595</v>
+      </c>
+      <c r="J266" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>302</v>
+      </c>
+      <c r="B267" t="s">
+        <v>218</v>
+      </c>
+      <c r="H267" t="s">
+        <v>622</v>
+      </c>
+      <c r="J267" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>255</v>
+      </c>
+      <c r="B268" t="s">
+        <v>218</v>
+      </c>
+      <c r="H268" t="s">
+        <v>624</v>
+      </c>
+      <c r="J268" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>303</v>
+      </c>
+      <c r="B269" t="s">
+        <v>218</v>
+      </c>
+      <c r="H269" t="s">
+        <v>626</v>
+      </c>
+      <c r="J269" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>256</v>
+      </c>
+      <c r="B270" t="s">
+        <v>218</v>
+      </c>
+      <c r="H270" t="s">
+        <v>628</v>
+      </c>
+      <c r="J270" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>304</v>
+      </c>
+      <c r="B271" t="s">
+        <v>218</v>
+      </c>
+      <c r="H271" t="s">
+        <v>655</v>
+      </c>
+      <c r="J271" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H272" t="s">
+        <v>657</v>
+      </c>
+      <c r="J272" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="273" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H273" t="s">
+        <v>659</v>
+      </c>
+      <c r="J273" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="274" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H274" t="s">
+        <v>661</v>
+      </c>
+      <c r="J274" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="275" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H275" t="s">
+        <v>688</v>
+      </c>
+      <c r="J275" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="276" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H276" t="s">
+        <v>690</v>
+      </c>
+      <c r="J276" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="277" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H277" t="s">
+        <v>692</v>
+      </c>
+      <c r="J277" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="278" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H278" t="s">
+        <v>694</v>
+      </c>
+      <c r="J278" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="279" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H279" t="s">
+        <v>28</v>
+      </c>
+      <c r="J279" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="280" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H280" t="s">
+        <v>31</v>
+      </c>
+      <c r="J280" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="281" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H281" t="s">
+        <v>33</v>
+      </c>
+      <c r="J281" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="282" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H282" t="s">
+        <v>35</v>
+      </c>
+      <c r="J282" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="283" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H283" t="s">
+        <v>64</v>
+      </c>
+      <c r="J283" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="284" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H284" t="s">
+        <v>66</v>
+      </c>
+      <c r="J284" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="285" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H285" t="s">
+        <v>68</v>
+      </c>
+      <c r="J285" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="286" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H286" t="s">
+        <v>70</v>
+      </c>
+      <c r="J286" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="287" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H287" t="s">
+        <v>98</v>
+      </c>
+      <c r="J287" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="288" spans="8:10" x14ac:dyDescent="0.3">
+      <c r="H288" t="s">
+        <v>100</v>
+      </c>
+      <c r="J288" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H289" t="s">
+        <v>102</v>
+      </c>
+      <c r="J289" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H290" t="s">
+        <v>104</v>
+      </c>
+      <c r="J290" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H291" t="s">
+        <v>132</v>
+      </c>
+      <c r="J291" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H292" t="s">
+        <v>134</v>
+      </c>
+      <c r="J292" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A293" s="1"/>
+      <c r="H293" t="s">
+        <v>136</v>
+      </c>
+      <c r="J293" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A294" s="1"/>
+      <c r="H294" t="s">
+        <v>138</v>
+      </c>
+      <c r="J294" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A295" s="1"/>
+      <c r="H295" t="s">
+        <v>166</v>
+      </c>
+      <c r="J295" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A296" s="1"/>
+      <c r="H296" t="s">
+        <v>168</v>
+      </c>
+      <c r="J296" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A297" s="1"/>
+      <c r="H297" t="s">
+        <v>170</v>
+      </c>
+      <c r="J297" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H298" t="s">
+        <v>172</v>
+      </c>
+      <c r="J298" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H299" t="s">
+        <v>200</v>
+      </c>
+      <c r="J299" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A300" s="1"/>
+      <c r="H300" t="s">
+        <v>202</v>
+      </c>
+      <c r="J300" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A301" s="1"/>
+      <c r="H301" t="s">
+        <v>204</v>
+      </c>
+      <c r="J301" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A302" s="1"/>
+      <c r="H302" t="s">
+        <v>206</v>
+      </c>
+      <c r="J302" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B313">
+    <sortCondition ref="B2:B313"/>
+    <sortCondition ref="A2:A313"/>
+  </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>